--- a/templates/勤務説明書.xlsx
+++ b/templates/勤務説明書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hatsu\Desktop\anken-kanri\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0857AD-9F92-43FB-A100-C4B1E4A8B098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{259E3D09-2A23-43DD-966C-55321E2AE38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{32DF5ADC-5A0A-45FE-B261-2C6E0FFBD8BF}"/>
   </bookViews>
@@ -2477,43 +2477,535 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="6" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="6" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2522,68 +3014,56 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2594,632 +3074,152 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="57" fontId="6" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="57" fontId="6" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3616,268 +3616,268 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="160" t="s">
+      <c r="B1" s="262" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
-      <c r="L1" s="160"/>
-      <c r="M1" s="160"/>
-      <c r="N1" s="160"/>
-      <c r="O1" s="160"/>
-      <c r="P1" s="160"/>
-      <c r="Q1" s="160"/>
-      <c r="R1" s="160"/>
-      <c r="S1" s="160"/>
-      <c r="T1" s="160"/>
-      <c r="U1" s="160"/>
-      <c r="V1" s="160"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="262"/>
+      <c r="I1" s="262"/>
+      <c r="J1" s="262"/>
+      <c r="K1" s="262"/>
+      <c r="L1" s="262"/>
+      <c r="M1" s="262"/>
+      <c r="N1" s="262"/>
+      <c r="O1" s="262"/>
+      <c r="P1" s="262"/>
+      <c r="Q1" s="262"/>
+      <c r="R1" s="262"/>
+      <c r="S1" s="262"/>
+      <c r="T1" s="262"/>
+      <c r="U1" s="262"/>
+      <c r="V1" s="262"/>
     </row>
     <row r="2" spans="2:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="161"/>
-      <c r="C2" s="161"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="162" t="s">
+      <c r="B2" s="263"/>
+      <c r="C2" s="263"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="164"/>
+      <c r="I2" s="164"/>
+      <c r="J2" s="164"/>
+      <c r="K2" s="164"/>
+      <c r="L2" s="164"/>
+      <c r="M2" s="164"/>
+      <c r="N2" s="264" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="162"/>
-      <c r="P2" s="162"/>
-      <c r="Q2" s="162"/>
-      <c r="R2" s="128"/>
-      <c r="S2" s="128"/>
-      <c r="T2" s="163">
+      <c r="O2" s="264"/>
+      <c r="P2" s="264"/>
+      <c r="Q2" s="264"/>
+      <c r="R2" s="164"/>
+      <c r="S2" s="164"/>
+      <c r="T2" s="265">
         <f ca="1">TODAY()</f>
-        <v>46293</v>
-      </c>
-      <c r="U2" s="128"/>
+        <v>46295</v>
+      </c>
+      <c r="U2" s="164"/>
       <c r="V2" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="113" t="s">
+      <c r="B3" s="249" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="190" t="s">
+      <c r="C3" s="256"/>
+      <c r="D3" s="109" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="191"/>
-      <c r="F3" s="191"/>
-      <c r="G3" s="191"/>
-      <c r="H3" s="191"/>
-      <c r="I3" s="191"/>
-      <c r="J3" s="191" t="s">
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105" t="s">
         <v>124</v>
       </c>
-      <c r="K3" s="191"/>
-      <c r="L3" s="191"/>
-      <c r="M3" s="192"/>
-      <c r="N3" s="180" t="s">
+      <c r="K3" s="105"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="246" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="113" t="s">
+      <c r="O3" s="249" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="183" t="s">
+      <c r="P3" s="250"/>
+      <c r="Q3" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="R3" s="184"/>
-      <c r="S3" s="184"/>
-      <c r="T3" s="184"/>
-      <c r="U3" s="164"/>
-      <c r="V3" s="165"/>
+      <c r="R3" s="252"/>
+      <c r="S3" s="252"/>
+      <c r="T3" s="252"/>
+      <c r="U3" s="239"/>
+      <c r="V3" s="240"/>
     </row>
     <row r="4" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="116"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="193"/>
-      <c r="E4" s="194"/>
-      <c r="F4" s="194"/>
-      <c r="G4" s="194"/>
-      <c r="H4" s="194"/>
-      <c r="I4" s="194"/>
-      <c r="J4" s="194"/>
-      <c r="K4" s="194"/>
-      <c r="L4" s="194"/>
-      <c r="M4" s="195"/>
-      <c r="N4" s="181"/>
-      <c r="O4" s="166" t="s">
+      <c r="B4" s="224"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="107"/>
+      <c r="M4" s="108"/>
+      <c r="N4" s="247"/>
+      <c r="O4" s="218" t="s">
         <v>1</v>
       </c>
-      <c r="P4" s="167"/>
-      <c r="Q4" s="168" t="s">
+      <c r="P4" s="219"/>
+      <c r="Q4" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="R4" s="169"/>
-      <c r="S4" s="169"/>
-      <c r="T4" s="169"/>
-      <c r="U4" s="169"/>
-      <c r="V4" s="170"/>
+      <c r="R4" s="267"/>
+      <c r="S4" s="267"/>
+      <c r="T4" s="267"/>
+      <c r="U4" s="267"/>
+      <c r="V4" s="268"/>
     </row>
     <row r="5" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="113" t="s">
+      <c r="B5" s="249" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="190" t="s">
+      <c r="C5" s="256"/>
+      <c r="D5" s="109" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="191"/>
-      <c r="F5" s="191"/>
-      <c r="G5" s="191"/>
-      <c r="H5" s="191"/>
-      <c r="I5" s="191"/>
-      <c r="J5" s="191"/>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="192"/>
-      <c r="N5" s="181"/>
-      <c r="O5" s="166"/>
-      <c r="P5" s="167"/>
-      <c r="Q5" s="171"/>
-      <c r="R5" s="172"/>
-      <c r="S5" s="172"/>
-      <c r="T5" s="172"/>
-      <c r="U5" s="172"/>
-      <c r="V5" s="173"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="247"/>
+      <c r="O5" s="218"/>
+      <c r="P5" s="219"/>
+      <c r="Q5" s="269"/>
+      <c r="R5" s="270"/>
+      <c r="S5" s="270"/>
+      <c r="T5" s="270"/>
+      <c r="U5" s="270"/>
+      <c r="V5" s="271"/>
     </row>
     <row r="6" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="116"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="193"/>
-      <c r="E6" s="194"/>
-      <c r="F6" s="194"/>
-      <c r="G6" s="194"/>
-      <c r="H6" s="194"/>
-      <c r="I6" s="194"/>
-      <c r="J6" s="194"/>
-      <c r="K6" s="194"/>
-      <c r="L6" s="194"/>
-      <c r="M6" s="195"/>
-      <c r="N6" s="181"/>
-      <c r="O6" s="166" t="s">
+      <c r="B6" s="224"/>
+      <c r="C6" s="257"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="107"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="247"/>
+      <c r="O6" s="218" t="s">
         <v>73</v>
       </c>
-      <c r="P6" s="167"/>
-      <c r="Q6" s="177" t="s">
+      <c r="P6" s="219"/>
+      <c r="Q6" s="243" t="s">
         <v>117</v>
       </c>
-      <c r="R6" s="178"/>
-      <c r="S6" s="178"/>
-      <c r="T6" s="178"/>
-      <c r="U6" s="178"/>
-      <c r="V6" s="179"/>
+      <c r="R6" s="244"/>
+      <c r="S6" s="244"/>
+      <c r="T6" s="244"/>
+      <c r="U6" s="244"/>
+      <c r="V6" s="245"/>
     </row>
     <row r="7" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="113" t="s">
+      <c r="B7" s="249" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="114"/>
-      <c r="D7" s="190" t="s">
+      <c r="C7" s="256"/>
+      <c r="D7" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="191"/>
-      <c r="F7" s="191"/>
-      <c r="G7" s="191" t="s">
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105" t="s">
         <v>126</v>
       </c>
-      <c r="H7" s="191"/>
-      <c r="I7" s="174" t="s">
+      <c r="H7" s="105"/>
+      <c r="I7" s="238" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="164"/>
-      <c r="K7" s="164"/>
-      <c r="L7" s="164"/>
-      <c r="M7" s="165"/>
-      <c r="N7" s="181"/>
-      <c r="O7" s="166" t="s">
+      <c r="J7" s="239"/>
+      <c r="K7" s="239"/>
+      <c r="L7" s="239"/>
+      <c r="M7" s="240"/>
+      <c r="N7" s="247"/>
+      <c r="O7" s="218" t="s">
         <v>67</v>
       </c>
-      <c r="P7" s="167"/>
-      <c r="Q7" s="177" t="s">
+      <c r="P7" s="219"/>
+      <c r="Q7" s="243" t="s">
         <v>118</v>
       </c>
-      <c r="R7" s="178"/>
-      <c r="S7" s="178"/>
-      <c r="T7" s="178"/>
-      <c r="U7" s="178"/>
-      <c r="V7" s="179"/>
+      <c r="R7" s="244"/>
+      <c r="S7" s="244"/>
+      <c r="T7" s="244"/>
+      <c r="U7" s="244"/>
+      <c r="V7" s="245"/>
     </row>
     <row r="8" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="116"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="193"/>
-      <c r="E8" s="194"/>
-      <c r="F8" s="194"/>
-      <c r="G8" s="194"/>
-      <c r="H8" s="194"/>
-      <c r="I8" s="175"/>
-      <c r="J8" s="175"/>
-      <c r="K8" s="175"/>
-      <c r="L8" s="175"/>
-      <c r="M8" s="176"/>
-      <c r="N8" s="182"/>
-      <c r="O8" s="116" t="s">
+      <c r="B8" s="224"/>
+      <c r="C8" s="257"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="107"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="241"/>
+      <c r="K8" s="241"/>
+      <c r="L8" s="241"/>
+      <c r="M8" s="242"/>
+      <c r="N8" s="248"/>
+      <c r="O8" s="224" t="s">
         <v>31</v>
       </c>
-      <c r="P8" s="118"/>
-      <c r="Q8" s="196" t="s">
+      <c r="P8" s="225"/>
+      <c r="Q8" s="258" t="s">
         <v>128</v>
       </c>
-      <c r="R8" s="197"/>
-      <c r="S8" s="66" t="s">
+      <c r="R8" s="259"/>
+      <c r="S8" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="T8" s="198" t="s">
+      <c r="T8" s="260" t="s">
         <v>129</v>
       </c>
-      <c r="U8" s="198"/>
-      <c r="V8" s="199"/>
+      <c r="U8" s="260"/>
+      <c r="V8" s="261"/>
     </row>
     <row r="9" spans="2:22" s="2" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="185" t="s">
+      <c r="B9" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="186"/>
-      <c r="D9" s="187" t="s">
+      <c r="C9" s="128"/>
+      <c r="D9" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="E9" s="188"/>
-      <c r="F9" s="188"/>
-      <c r="G9" s="188"/>
-      <c r="H9" s="188"/>
-      <c r="I9" s="188"/>
-      <c r="J9" s="188"/>
-      <c r="K9" s="188"/>
-      <c r="L9" s="188"/>
-      <c r="M9" s="188"/>
-      <c r="N9" s="188"/>
-      <c r="O9" s="188"/>
-      <c r="P9" s="188"/>
-      <c r="Q9" s="188"/>
-      <c r="R9" s="188"/>
-      <c r="S9" s="188"/>
-      <c r="T9" s="188"/>
-      <c r="U9" s="188"/>
-      <c r="V9" s="189"/>
+      <c r="E9" s="254"/>
+      <c r="F9" s="254"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="254"/>
+      <c r="I9" s="254"/>
+      <c r="J9" s="254"/>
+      <c r="K9" s="254"/>
+      <c r="L9" s="254"/>
+      <c r="M9" s="254"/>
+      <c r="N9" s="254"/>
+      <c r="O9" s="254"/>
+      <c r="P9" s="254"/>
+      <c r="Q9" s="254"/>
+      <c r="R9" s="254"/>
+      <c r="S9" s="254"/>
+      <c r="T9" s="254"/>
+      <c r="U9" s="254"/>
+      <c r="V9" s="255"/>
     </row>
     <row r="10" spans="2:22" s="2" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3"/>
@@ -3903,81 +3903,81 @@
       <c r="V10" s="3"/>
     </row>
     <row r="11" spans="2:22" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="200" t="s">
+      <c r="B11" s="290" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="203" t="s">
+      <c r="C11" s="230" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="204"/>
-      <c r="E11" s="205" t="s">
+      <c r="D11" s="231"/>
+      <c r="E11" s="232" t="s">
         <v>137</v>
       </c>
-      <c r="F11" s="138"/>
-      <c r="G11" s="138"/>
-      <c r="H11" s="138"/>
-      <c r="I11" s="138"/>
-      <c r="J11" s="138"/>
-      <c r="K11" s="138"/>
-      <c r="L11" s="206"/>
-      <c r="M11" s="203" t="s">
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="125"/>
+      <c r="K11" s="125"/>
+      <c r="L11" s="233"/>
+      <c r="M11" s="230" t="s">
         <v>70</v>
       </c>
-      <c r="N11" s="204"/>
-      <c r="O11" s="205" t="s">
+      <c r="N11" s="231"/>
+      <c r="O11" s="232" t="s">
         <v>138</v>
       </c>
-      <c r="P11" s="138"/>
-      <c r="Q11" s="138"/>
-      <c r="R11" s="138"/>
-      <c r="S11" s="138"/>
-      <c r="T11" s="138"/>
-      <c r="U11" s="138"/>
-      <c r="V11" s="206"/>
+      <c r="P11" s="125"/>
+      <c r="Q11" s="125"/>
+      <c r="R11" s="125"/>
+      <c r="S11" s="125"/>
+      <c r="T11" s="125"/>
+      <c r="U11" s="125"/>
+      <c r="V11" s="233"/>
     </row>
     <row r="12" spans="2:22" s="2" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="201"/>
-      <c r="C12" s="209" t="s">
+      <c r="B12" s="291"/>
+      <c r="C12" s="204" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="210"/>
-      <c r="E12" s="211" t="s">
+      <c r="D12" s="208"/>
+      <c r="E12" s="236" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="207"/>
-      <c r="G12" s="207" t="s">
+      <c r="F12" s="237"/>
+      <c r="G12" s="237" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="207"/>
-      <c r="I12" s="208" t="s">
+      <c r="H12" s="237"/>
+      <c r="I12" s="229" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="208"/>
+      <c r="J12" s="229"/>
       <c r="K12" s="17"/>
-      <c r="L12" s="62" t="s">
+      <c r="L12" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="209" t="s">
+      <c r="M12" s="204" t="s">
         <v>32</v>
       </c>
-      <c r="N12" s="210"/>
-      <c r="O12" s="211"/>
-      <c r="P12" s="207"/>
-      <c r="Q12" s="207"/>
-      <c r="R12" s="207"/>
-      <c r="S12" s="208"/>
-      <c r="T12" s="208"/>
+      <c r="N12" s="208"/>
+      <c r="O12" s="236"/>
+      <c r="P12" s="237"/>
+      <c r="Q12" s="237"/>
+      <c r="R12" s="237"/>
+      <c r="S12" s="229"/>
+      <c r="T12" s="229"/>
       <c r="U12" s="17"/>
-      <c r="V12" s="62"/>
+      <c r="V12" s="61"/>
     </row>
     <row r="13" spans="2:22" s="2" customFormat="1" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="201"/>
-      <c r="C13" s="99" t="s">
+      <c r="B13" s="291"/>
+      <c r="C13" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="101"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
+      <c r="D13" s="235"/>
+      <c r="E13" s="164"/>
+      <c r="F13" s="164"/>
       <c r="G13" s="18" t="s">
         <v>8</v>
       </c>
@@ -3986,27 +3986,27 @@
       </c>
       <c r="J13" s="8"/>
       <c r="L13" s="19"/>
-      <c r="M13" s="99" t="s">
+      <c r="M13" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="N13" s="101"/>
-      <c r="O13" s="128"/>
-      <c r="P13" s="128"/>
+      <c r="N13" s="235"/>
+      <c r="O13" s="164"/>
+      <c r="P13" s="164"/>
       <c r="Q13" s="18"/>
       <c r="S13" s="8"/>
       <c r="T13" s="8"/>
       <c r="V13" s="19"/>
     </row>
     <row r="14" spans="2:22" s="2" customFormat="1" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="201"/>
-      <c r="C14" s="166" t="s">
+      <c r="B14" s="291"/>
+      <c r="C14" s="218" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="167"/>
-      <c r="E14" s="212">
+      <c r="D14" s="219"/>
+      <c r="E14" s="220">
         <v>18</v>
       </c>
-      <c r="F14" s="213"/>
+      <c r="F14" s="221"/>
       <c r="G14" s="4" t="s">
         <v>58</v>
       </c>
@@ -4016,846 +4016,846 @@
       <c r="I14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="214" t="s">
+      <c r="J14" s="222" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="214"/>
-      <c r="L14" s="215"/>
-      <c r="M14" s="166" t="s">
+      <c r="K14" s="222"/>
+      <c r="L14" s="223"/>
+      <c r="M14" s="218" t="s">
         <v>23</v>
       </c>
-      <c r="N14" s="167"/>
-      <c r="O14" s="212"/>
-      <c r="P14" s="213"/>
+      <c r="N14" s="219"/>
+      <c r="O14" s="220"/>
+      <c r="P14" s="221"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="214"/>
-      <c r="U14" s="214"/>
-      <c r="V14" s="215"/>
+      <c r="T14" s="222"/>
+      <c r="U14" s="222"/>
+      <c r="V14" s="223"/>
     </row>
     <row r="15" spans="2:22" s="2" customFormat="1" ht="14.1" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="201"/>
-      <c r="C15" s="116" t="s">
+      <c r="B15" s="291"/>
+      <c r="C15" s="224" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="118"/>
-      <c r="E15" s="216" t="s">
+      <c r="D15" s="225"/>
+      <c r="E15" s="226" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="217"/>
-      <c r="G15" s="217"/>
-      <c r="H15" s="217"/>
-      <c r="I15" s="217"/>
-      <c r="J15" s="217"/>
-      <c r="K15" s="217"/>
-      <c r="L15" s="218"/>
-      <c r="M15" s="116" t="s">
+      <c r="F15" s="227"/>
+      <c r="G15" s="227"/>
+      <c r="H15" s="227"/>
+      <c r="I15" s="227"/>
+      <c r="J15" s="227"/>
+      <c r="K15" s="227"/>
+      <c r="L15" s="228"/>
+      <c r="M15" s="224" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="118"/>
-      <c r="O15" s="216"/>
-      <c r="P15" s="217"/>
-      <c r="Q15" s="217"/>
-      <c r="R15" s="217"/>
-      <c r="S15" s="217"/>
-      <c r="T15" s="217"/>
-      <c r="U15" s="217"/>
-      <c r="V15" s="218"/>
+      <c r="N15" s="225"/>
+      <c r="O15" s="226"/>
+      <c r="P15" s="227"/>
+      <c r="Q15" s="227"/>
+      <c r="R15" s="227"/>
+      <c r="S15" s="227"/>
+      <c r="T15" s="227"/>
+      <c r="U15" s="227"/>
+      <c r="V15" s="228"/>
     </row>
     <row r="16" spans="2:22" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="201"/>
-      <c r="C16" s="222" t="s">
+      <c r="B16" s="291"/>
+      <c r="C16" s="209" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="223"/>
-      <c r="E16" s="223"/>
-      <c r="F16" s="223"/>
-      <c r="G16" s="223"/>
-      <c r="H16" s="223"/>
-      <c r="I16" s="223"/>
-      <c r="J16" s="223"/>
-      <c r="K16" s="223"/>
-      <c r="L16" s="223"/>
-      <c r="M16" s="223"/>
-      <c r="N16" s="223"/>
-      <c r="O16" s="223"/>
-      <c r="P16" s="223"/>
-      <c r="Q16" s="223"/>
-      <c r="R16" s="223"/>
-      <c r="S16" s="223"/>
-      <c r="T16" s="223"/>
-      <c r="U16" s="223"/>
-      <c r="V16" s="224"/>
+      <c r="D16" s="210"/>
+      <c r="E16" s="210"/>
+      <c r="F16" s="210"/>
+      <c r="G16" s="210"/>
+      <c r="H16" s="210"/>
+      <c r="I16" s="210"/>
+      <c r="J16" s="210"/>
+      <c r="K16" s="210"/>
+      <c r="L16" s="210"/>
+      <c r="M16" s="210"/>
+      <c r="N16" s="210"/>
+      <c r="O16" s="210"/>
+      <c r="P16" s="210"/>
+      <c r="Q16" s="210"/>
+      <c r="R16" s="210"/>
+      <c r="S16" s="210"/>
+      <c r="T16" s="210"/>
+      <c r="U16" s="210"/>
+      <c r="V16" s="211"/>
     </row>
     <row r="17" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="201"/>
-      <c r="C17" s="225" t="s">
+      <c r="B17" s="291"/>
+      <c r="C17" s="212" t="s">
         <v>140</v>
       </c>
-      <c r="D17" s="226"/>
-      <c r="E17" s="226"/>
-      <c r="F17" s="226"/>
-      <c r="G17" s="226"/>
-      <c r="H17" s="226"/>
-      <c r="I17" s="226"/>
-      <c r="J17" s="226"/>
-      <c r="K17" s="226"/>
-      <c r="L17" s="226"/>
-      <c r="M17" s="226"/>
-      <c r="N17" s="226"/>
-      <c r="O17" s="226"/>
-      <c r="P17" s="226"/>
-      <c r="Q17" s="226"/>
-      <c r="R17" s="226"/>
-      <c r="S17" s="226"/>
-      <c r="T17" s="226"/>
-      <c r="U17" s="226"/>
-      <c r="V17" s="227"/>
+      <c r="D17" s="213"/>
+      <c r="E17" s="213"/>
+      <c r="F17" s="213"/>
+      <c r="G17" s="213"/>
+      <c r="H17" s="213"/>
+      <c r="I17" s="213"/>
+      <c r="J17" s="213"/>
+      <c r="K17" s="213"/>
+      <c r="L17" s="213"/>
+      <c r="M17" s="213"/>
+      <c r="N17" s="213"/>
+      <c r="O17" s="213"/>
+      <c r="P17" s="213"/>
+      <c r="Q17" s="213"/>
+      <c r="R17" s="213"/>
+      <c r="S17" s="213"/>
+      <c r="T17" s="213"/>
+      <c r="U17" s="213"/>
+      <c r="V17" s="214"/>
     </row>
     <row r="18" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="201"/>
-      <c r="C18" s="228"/>
-      <c r="D18" s="229"/>
-      <c r="E18" s="229"/>
-      <c r="F18" s="229"/>
-      <c r="G18" s="229"/>
-      <c r="H18" s="229"/>
-      <c r="I18" s="229"/>
-      <c r="J18" s="229"/>
-      <c r="K18" s="229"/>
-      <c r="L18" s="229"/>
-      <c r="M18" s="229"/>
-      <c r="N18" s="229"/>
-      <c r="O18" s="229"/>
-      <c r="P18" s="229"/>
-      <c r="Q18" s="229"/>
-      <c r="R18" s="229"/>
-      <c r="S18" s="229"/>
-      <c r="T18" s="229"/>
-      <c r="U18" s="229"/>
-      <c r="V18" s="230"/>
+      <c r="B18" s="291"/>
+      <c r="C18" s="215"/>
+      <c r="D18" s="216"/>
+      <c r="E18" s="216"/>
+      <c r="F18" s="216"/>
+      <c r="G18" s="216"/>
+      <c r="H18" s="216"/>
+      <c r="I18" s="216"/>
+      <c r="J18" s="216"/>
+      <c r="K18" s="216"/>
+      <c r="L18" s="216"/>
+      <c r="M18" s="216"/>
+      <c r="N18" s="216"/>
+      <c r="O18" s="216"/>
+      <c r="P18" s="216"/>
+      <c r="Q18" s="216"/>
+      <c r="R18" s="216"/>
+      <c r="S18" s="216"/>
+      <c r="T18" s="216"/>
+      <c r="U18" s="216"/>
+      <c r="V18" s="217"/>
     </row>
     <row r="19" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="201"/>
-      <c r="C19" s="228"/>
-      <c r="D19" s="229"/>
-      <c r="E19" s="229"/>
-      <c r="F19" s="229"/>
-      <c r="G19" s="229"/>
-      <c r="H19" s="229"/>
-      <c r="I19" s="229"/>
-      <c r="J19" s="229"/>
-      <c r="K19" s="229"/>
-      <c r="L19" s="229"/>
-      <c r="M19" s="229"/>
-      <c r="N19" s="229"/>
-      <c r="O19" s="229"/>
-      <c r="P19" s="229"/>
-      <c r="Q19" s="229"/>
-      <c r="R19" s="229"/>
-      <c r="S19" s="229"/>
-      <c r="T19" s="229"/>
-      <c r="U19" s="229"/>
-      <c r="V19" s="230"/>
+      <c r="B19" s="291"/>
+      <c r="C19" s="215"/>
+      <c r="D19" s="216"/>
+      <c r="E19" s="216"/>
+      <c r="F19" s="216"/>
+      <c r="G19" s="216"/>
+      <c r="H19" s="216"/>
+      <c r="I19" s="216"/>
+      <c r="J19" s="216"/>
+      <c r="K19" s="216"/>
+      <c r="L19" s="216"/>
+      <c r="M19" s="216"/>
+      <c r="N19" s="216"/>
+      <c r="O19" s="216"/>
+      <c r="P19" s="216"/>
+      <c r="Q19" s="216"/>
+      <c r="R19" s="216"/>
+      <c r="S19" s="216"/>
+      <c r="T19" s="216"/>
+      <c r="U19" s="216"/>
+      <c r="V19" s="217"/>
     </row>
     <row r="20" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="201"/>
-      <c r="C20" s="228"/>
-      <c r="D20" s="229"/>
-      <c r="E20" s="229"/>
-      <c r="F20" s="229"/>
-      <c r="G20" s="229"/>
-      <c r="H20" s="229"/>
-      <c r="I20" s="229"/>
-      <c r="J20" s="229"/>
-      <c r="K20" s="229"/>
-      <c r="L20" s="229"/>
-      <c r="M20" s="229"/>
-      <c r="N20" s="229"/>
-      <c r="O20" s="229"/>
-      <c r="P20" s="229"/>
-      <c r="Q20" s="229"/>
-      <c r="R20" s="229"/>
-      <c r="S20" s="229"/>
-      <c r="T20" s="229"/>
-      <c r="U20" s="229"/>
-      <c r="V20" s="230"/>
+      <c r="B20" s="291"/>
+      <c r="C20" s="215"/>
+      <c r="D20" s="216"/>
+      <c r="E20" s="216"/>
+      <c r="F20" s="216"/>
+      <c r="G20" s="216"/>
+      <c r="H20" s="216"/>
+      <c r="I20" s="216"/>
+      <c r="J20" s="216"/>
+      <c r="K20" s="216"/>
+      <c r="L20" s="216"/>
+      <c r="M20" s="216"/>
+      <c r="N20" s="216"/>
+      <c r="O20" s="216"/>
+      <c r="P20" s="216"/>
+      <c r="Q20" s="216"/>
+      <c r="R20" s="216"/>
+      <c r="S20" s="216"/>
+      <c r="T20" s="216"/>
+      <c r="U20" s="216"/>
+      <c r="V20" s="217"/>
     </row>
     <row r="21" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="201"/>
-      <c r="C21" s="228"/>
-      <c r="D21" s="229"/>
-      <c r="E21" s="229"/>
-      <c r="F21" s="229"/>
-      <c r="G21" s="229"/>
-      <c r="H21" s="229"/>
-      <c r="I21" s="229"/>
-      <c r="J21" s="229"/>
-      <c r="K21" s="229"/>
-      <c r="L21" s="229"/>
-      <c r="M21" s="229"/>
-      <c r="N21" s="229"/>
-      <c r="O21" s="229"/>
-      <c r="P21" s="229"/>
-      <c r="Q21" s="229"/>
-      <c r="R21" s="229"/>
-      <c r="S21" s="229"/>
-      <c r="T21" s="229"/>
-      <c r="U21" s="229"/>
-      <c r="V21" s="230"/>
+      <c r="B21" s="291"/>
+      <c r="C21" s="215"/>
+      <c r="D21" s="216"/>
+      <c r="E21" s="216"/>
+      <c r="F21" s="216"/>
+      <c r="G21" s="216"/>
+      <c r="H21" s="216"/>
+      <c r="I21" s="216"/>
+      <c r="J21" s="216"/>
+      <c r="K21" s="216"/>
+      <c r="L21" s="216"/>
+      <c r="M21" s="216"/>
+      <c r="N21" s="216"/>
+      <c r="O21" s="216"/>
+      <c r="P21" s="216"/>
+      <c r="Q21" s="216"/>
+      <c r="R21" s="216"/>
+      <c r="S21" s="216"/>
+      <c r="T21" s="216"/>
+      <c r="U21" s="216"/>
+      <c r="V21" s="217"/>
     </row>
     <row r="22" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="201"/>
-      <c r="C22" s="228"/>
-      <c r="D22" s="229"/>
-      <c r="E22" s="229"/>
-      <c r="F22" s="229"/>
-      <c r="G22" s="229"/>
-      <c r="H22" s="229"/>
-      <c r="I22" s="229"/>
-      <c r="J22" s="229"/>
-      <c r="K22" s="229"/>
-      <c r="L22" s="229"/>
-      <c r="M22" s="229"/>
-      <c r="N22" s="229"/>
-      <c r="O22" s="229"/>
-      <c r="P22" s="229"/>
-      <c r="Q22" s="229"/>
-      <c r="R22" s="229"/>
-      <c r="S22" s="229"/>
-      <c r="T22" s="229"/>
-      <c r="U22" s="229"/>
-      <c r="V22" s="230"/>
+      <c r="B22" s="291"/>
+      <c r="C22" s="215"/>
+      <c r="D22" s="216"/>
+      <c r="E22" s="216"/>
+      <c r="F22" s="216"/>
+      <c r="G22" s="216"/>
+      <c r="H22" s="216"/>
+      <c r="I22" s="216"/>
+      <c r="J22" s="216"/>
+      <c r="K22" s="216"/>
+      <c r="L22" s="216"/>
+      <c r="M22" s="216"/>
+      <c r="N22" s="216"/>
+      <c r="O22" s="216"/>
+      <c r="P22" s="216"/>
+      <c r="Q22" s="216"/>
+      <c r="R22" s="216"/>
+      <c r="S22" s="216"/>
+      <c r="T22" s="216"/>
+      <c r="U22" s="216"/>
+      <c r="V22" s="217"/>
     </row>
     <row r="23" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="201"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="94"/>
-      <c r="E23" s="94" t="s">
+      <c r="B23" s="291"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="F23" s="94"/>
-      <c r="G23" s="94" t="s">
+      <c r="F23" s="93"/>
+      <c r="G23" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="H23" s="94"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="94" t="s">
+      <c r="H23" s="93"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="94"/>
-      <c r="N23" s="94"/>
-      <c r="O23" s="94" t="s">
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="93"/>
+      <c r="N23" s="93"/>
+      <c r="O23" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="P23" s="94"/>
-      <c r="Q23" s="94" t="s">
+      <c r="P23" s="93"/>
+      <c r="Q23" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="R23" s="94"/>
-      <c r="S23" s="94"/>
-      <c r="T23" s="94" t="s">
+      <c r="R23" s="93"/>
+      <c r="S23" s="93"/>
+      <c r="T23" s="93" t="s">
         <v>51</v>
       </c>
-      <c r="U23" s="94"/>
-      <c r="V23" s="95"/>
+      <c r="U23" s="93"/>
+      <c r="V23" s="94"/>
     </row>
     <row r="24" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="201"/>
-      <c r="C24" s="209" t="s">
+      <c r="B24" s="291"/>
+      <c r="C24" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="219"/>
-      <c r="E24" s="219"/>
-      <c r="F24" s="219"/>
-      <c r="G24" s="219"/>
-      <c r="H24" s="219"/>
-      <c r="I24" s="220" t="s">
+      <c r="D24" s="205"/>
+      <c r="E24" s="205"/>
+      <c r="F24" s="205"/>
+      <c r="G24" s="205"/>
+      <c r="H24" s="205"/>
+      <c r="I24" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="221"/>
-      <c r="K24" s="219" t="s">
+      <c r="J24" s="207"/>
+      <c r="K24" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="210"/>
-      <c r="M24" s="209" t="s">
+      <c r="L24" s="208"/>
+      <c r="M24" s="204" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="219"/>
-      <c r="O24" s="219"/>
-      <c r="P24" s="219"/>
-      <c r="Q24" s="219"/>
-      <c r="R24" s="219"/>
-      <c r="S24" s="220" t="s">
+      <c r="N24" s="205"/>
+      <c r="O24" s="205"/>
+      <c r="P24" s="205"/>
+      <c r="Q24" s="205"/>
+      <c r="R24" s="205"/>
+      <c r="S24" s="206" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="221"/>
-      <c r="U24" s="219" t="s">
+      <c r="T24" s="207"/>
+      <c r="U24" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="V24" s="210"/>
+      <c r="V24" s="208"/>
     </row>
     <row r="25" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="201"/>
+      <c r="B25" s="291"/>
       <c r="C25" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="112">
+      <c r="D25" s="196">
         <v>0.33333333333333331</v>
       </c>
-      <c r="E25" s="112"/>
+      <c r="E25" s="196"/>
       <c r="F25" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="G25" s="142">
+      <c r="G25" s="197">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H25" s="143"/>
-      <c r="I25" s="144" t="s">
+      <c r="H25" s="198"/>
+      <c r="I25" s="199" t="s">
         <v>131</v>
       </c>
-      <c r="J25" s="146" t="s">
+      <c r="J25" s="190" t="s">
         <v>59</v>
       </c>
-      <c r="K25" s="108" t="s">
+      <c r="K25" s="192" t="s">
         <v>114</v>
       </c>
-      <c r="L25" s="110" t="s">
+      <c r="L25" s="194" t="s">
         <v>60</v>
       </c>
       <c r="M25" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="N25" s="112">
+      <c r="N25" s="196">
         <v>0.33333333333333331</v>
       </c>
-      <c r="O25" s="112"/>
+      <c r="O25" s="196"/>
       <c r="P25" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="Q25" s="142">
+      <c r="Q25" s="197">
         <v>0.70833333333333337</v>
       </c>
-      <c r="R25" s="143"/>
-      <c r="S25" s="144" t="s">
+      <c r="R25" s="198"/>
+      <c r="S25" s="199" t="s">
         <v>131</v>
       </c>
-      <c r="T25" s="146" t="s">
+      <c r="T25" s="190" t="s">
         <v>59</v>
       </c>
-      <c r="U25" s="108" t="s">
+      <c r="U25" s="192" t="s">
         <v>114</v>
       </c>
-      <c r="V25" s="110" t="s">
+      <c r="V25" s="194" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="2:22" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="201"/>
+      <c r="B26" s="291"/>
       <c r="C26" s="21"/>
       <c r="D26" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E26" s="58">
+      <c r="E26" s="57">
         <v>0.5</v>
       </c>
       <c r="F26" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="G26" s="59">
+      <c r="G26" s="58">
         <v>0.54166666666666663</v>
       </c>
       <c r="H26" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="I26" s="145"/>
-      <c r="J26" s="147"/>
-      <c r="K26" s="109"/>
-      <c r="L26" s="111"/>
+      <c r="I26" s="200"/>
+      <c r="J26" s="191"/>
+      <c r="K26" s="201"/>
+      <c r="L26" s="202"/>
       <c r="M26" s="21"/>
       <c r="N26" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="O26" s="58">
+      <c r="O26" s="57">
         <v>0.5</v>
       </c>
       <c r="P26" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="Q26" s="59">
+      <c r="Q26" s="58">
         <v>0.54166666666666663</v>
       </c>
       <c r="R26" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="S26" s="145"/>
-      <c r="T26" s="147"/>
-      <c r="U26" s="109"/>
-      <c r="V26" s="111"/>
+      <c r="S26" s="200"/>
+      <c r="T26" s="191"/>
+      <c r="U26" s="201"/>
+      <c r="V26" s="202"/>
     </row>
     <row r="27" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="201"/>
+      <c r="B27" s="291"/>
       <c r="C27" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="231">
+      <c r="D27" s="203">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E27" s="231"/>
+      <c r="E27" s="203"/>
       <c r="F27" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G27" s="142">
+      <c r="G27" s="197">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="H27" s="143"/>
-      <c r="I27" s="144" t="s">
+      <c r="H27" s="198"/>
+      <c r="I27" s="199" t="s">
         <v>133</v>
       </c>
-      <c r="J27" s="146" t="s">
+      <c r="J27" s="190" t="s">
         <v>59</v>
       </c>
-      <c r="K27" s="108" t="s">
+      <c r="K27" s="192" t="s">
         <v>132</v>
       </c>
-      <c r="L27" s="110" t="s">
+      <c r="L27" s="194" t="s">
         <v>60</v>
       </c>
       <c r="M27" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="N27" s="231">
+      <c r="N27" s="203">
         <v>0.70833333333333337</v>
       </c>
-      <c r="O27" s="231"/>
+      <c r="O27" s="203"/>
       <c r="P27" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="Q27" s="142">
+      <c r="Q27" s="197">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="R27" s="143"/>
-      <c r="S27" s="144" t="s">
+      <c r="R27" s="198"/>
+      <c r="S27" s="199" t="s">
         <v>133</v>
       </c>
-      <c r="T27" s="146" t="s">
+      <c r="T27" s="190" t="s">
         <v>59</v>
       </c>
-      <c r="U27" s="108" t="s">
+      <c r="U27" s="192" t="s">
         <v>132</v>
       </c>
-      <c r="V27" s="110" t="s">
+      <c r="V27" s="194" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="28" spans="2:22" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="201"/>
+      <c r="B28" s="291"/>
       <c r="C28" s="27"/>
       <c r="D28" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E28" s="60">
+      <c r="E28" s="59">
         <v>0.83333333333333337</v>
       </c>
       <c r="F28" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="G28" s="61">
+      <c r="G28" s="60">
         <v>0.86458333333333337</v>
       </c>
       <c r="H28" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="145"/>
-      <c r="J28" s="147"/>
-      <c r="K28" s="232"/>
-      <c r="L28" s="233"/>
+      <c r="I28" s="200"/>
+      <c r="J28" s="191"/>
+      <c r="K28" s="193"/>
+      <c r="L28" s="195"/>
       <c r="M28" s="27"/>
       <c r="N28" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="O28" s="60">
+      <c r="O28" s="59">
         <v>0.83333333333333337</v>
       </c>
       <c r="P28" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="Q28" s="61">
+      <c r="Q28" s="60">
         <v>0.86458333333333337</v>
       </c>
       <c r="R28" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="S28" s="145"/>
-      <c r="T28" s="147"/>
-      <c r="U28" s="232"/>
-      <c r="V28" s="233"/>
+      <c r="S28" s="200"/>
+      <c r="T28" s="191"/>
+      <c r="U28" s="193"/>
+      <c r="V28" s="195"/>
     </row>
     <row r="29" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="201"/>
+      <c r="B29" s="291"/>
       <c r="C29" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="112">
+      <c r="D29" s="196">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="E29" s="112"/>
+      <c r="E29" s="196"/>
       <c r="F29" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="G29" s="142">
+      <c r="G29" s="197">
         <v>0.33333333333333331</v>
       </c>
-      <c r="H29" s="143"/>
-      <c r="I29" s="144" t="s">
+      <c r="H29" s="198"/>
+      <c r="I29" s="199" t="s">
         <v>133</v>
       </c>
-      <c r="J29" s="146" t="s">
+      <c r="J29" s="190" t="s">
         <v>59</v>
       </c>
-      <c r="K29" s="108" t="s">
+      <c r="K29" s="192" t="s">
         <v>132</v>
       </c>
-      <c r="L29" s="110" t="s">
+      <c r="L29" s="194" t="s">
         <v>60</v>
       </c>
       <c r="M29" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="N29" s="112">
+      <c r="N29" s="196">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="O29" s="112"/>
+      <c r="O29" s="196"/>
       <c r="P29" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="Q29" s="142">
+      <c r="Q29" s="197">
         <v>0.33333333333333331</v>
       </c>
-      <c r="R29" s="143"/>
-      <c r="S29" s="144" t="s">
+      <c r="R29" s="198"/>
+      <c r="S29" s="199" t="s">
         <v>133</v>
       </c>
-      <c r="T29" s="146" t="s">
+      <c r="T29" s="190" t="s">
         <v>59</v>
       </c>
-      <c r="U29" s="108" t="s">
+      <c r="U29" s="192" t="s">
         <v>132</v>
       </c>
-      <c r="V29" s="110" t="s">
+      <c r="V29" s="194" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="30" spans="2:22" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="201"/>
+      <c r="B30" s="291"/>
       <c r="C30" s="21"/>
       <c r="D30" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E30" s="58">
+      <c r="E30" s="57">
         <v>0.14583333333333334</v>
       </c>
       <c r="F30" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="59">
+      <c r="G30" s="58">
         <v>0.17708333333333334</v>
       </c>
       <c r="H30" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="I30" s="145"/>
-      <c r="J30" s="147"/>
-      <c r="K30" s="109"/>
-      <c r="L30" s="111"/>
+      <c r="I30" s="200"/>
+      <c r="J30" s="191"/>
+      <c r="K30" s="201"/>
+      <c r="L30" s="202"/>
       <c r="M30" s="21"/>
       <c r="N30" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="O30" s="58">
+      <c r="O30" s="57">
         <v>0.14583333333333334</v>
       </c>
       <c r="P30" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="Q30" s="59">
+      <c r="Q30" s="58">
         <v>0.17708333333333334</v>
       </c>
       <c r="R30" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="S30" s="145"/>
-      <c r="T30" s="147"/>
-      <c r="U30" s="109"/>
-      <c r="V30" s="111"/>
+      <c r="S30" s="200"/>
+      <c r="T30" s="191"/>
+      <c r="U30" s="201"/>
+      <c r="V30" s="202"/>
     </row>
     <row r="31" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="201"/>
-      <c r="C31" s="131" t="s">
+      <c r="B31" s="291"/>
+      <c r="C31" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="132"/>
-      <c r="E31" s="133" t="s">
+      <c r="D31" s="281"/>
+      <c r="E31" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="F31" s="134"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="134"/>
-      <c r="J31" s="134"/>
-      <c r="K31" s="134"/>
-      <c r="L31" s="135"/>
-      <c r="M31" s="131" t="s">
+      <c r="F31" s="169"/>
+      <c r="G31" s="169"/>
+      <c r="H31" s="169"/>
+      <c r="I31" s="169"/>
+      <c r="J31" s="169"/>
+      <c r="K31" s="169"/>
+      <c r="L31" s="170"/>
+      <c r="M31" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="N31" s="253"/>
-      <c r="O31" s="133" t="s">
+      <c r="N31" s="184"/>
+      <c r="O31" s="168" t="s">
         <v>145</v>
       </c>
-      <c r="P31" s="134"/>
-      <c r="Q31" s="134"/>
-      <c r="R31" s="134"/>
-      <c r="S31" s="134"/>
-      <c r="T31" s="134"/>
-      <c r="U31" s="134"/>
-      <c r="V31" s="135"/>
+      <c r="P31" s="169"/>
+      <c r="Q31" s="169"/>
+      <c r="R31" s="169"/>
+      <c r="S31" s="169"/>
+      <c r="T31" s="169"/>
+      <c r="U31" s="169"/>
+      <c r="V31" s="170"/>
     </row>
     <row r="32" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="201"/>
-      <c r="C32" s="234" t="s">
+      <c r="B32" s="291"/>
+      <c r="C32" s="171" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="235"/>
-      <c r="E32" s="238" t="s">
+      <c r="D32" s="172"/>
+      <c r="E32" s="175" t="s">
         <v>134</v>
       </c>
-      <c r="F32" s="239"/>
-      <c r="G32" s="239"/>
-      <c r="H32" s="239"/>
-      <c r="I32" s="239"/>
-      <c r="J32" s="239"/>
-      <c r="K32" s="239"/>
-      <c r="L32" s="240"/>
-      <c r="M32" s="234" t="s">
+      <c r="F32" s="176"/>
+      <c r="G32" s="176"/>
+      <c r="H32" s="176"/>
+      <c r="I32" s="176"/>
+      <c r="J32" s="176"/>
+      <c r="K32" s="176"/>
+      <c r="L32" s="177"/>
+      <c r="M32" s="171" t="s">
         <v>52</v>
       </c>
-      <c r="N32" s="241"/>
-      <c r="O32" s="238" t="s">
+      <c r="N32" s="178"/>
+      <c r="O32" s="175" t="s">
         <v>134</v>
       </c>
-      <c r="P32" s="239"/>
-      <c r="Q32" s="239"/>
-      <c r="R32" s="239"/>
-      <c r="S32" s="239"/>
-      <c r="T32" s="239"/>
-      <c r="U32" s="239"/>
-      <c r="V32" s="240"/>
+      <c r="P32" s="176"/>
+      <c r="Q32" s="176"/>
+      <c r="R32" s="176"/>
+      <c r="S32" s="176"/>
+      <c r="T32" s="176"/>
+      <c r="U32" s="176"/>
+      <c r="V32" s="177"/>
     </row>
     <row r="33" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="201"/>
-      <c r="C33" s="236"/>
-      <c r="D33" s="237"/>
-      <c r="E33" s="243" t="s">
+      <c r="B33" s="291"/>
+      <c r="C33" s="173"/>
+      <c r="D33" s="174"/>
+      <c r="E33" s="180" t="s">
         <v>121</v>
       </c>
-      <c r="F33" s="244"/>
-      <c r="G33" s="244"/>
-      <c r="H33" s="244"/>
-      <c r="I33" s="244"/>
-      <c r="J33" s="244"/>
-      <c r="K33" s="244"/>
-      <c r="L33" s="245"/>
-      <c r="M33" s="236"/>
-      <c r="N33" s="242"/>
-      <c r="O33" s="243" t="s">
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="181"/>
+      <c r="L33" s="182"/>
+      <c r="M33" s="173"/>
+      <c r="N33" s="179"/>
+      <c r="O33" s="180" t="s">
         <v>121</v>
       </c>
-      <c r="P33" s="244"/>
-      <c r="Q33" s="244"/>
-      <c r="R33" s="244"/>
-      <c r="S33" s="244"/>
-      <c r="T33" s="244"/>
-      <c r="U33" s="244"/>
-      <c r="V33" s="245"/>
+      <c r="P33" s="181"/>
+      <c r="Q33" s="181"/>
+      <c r="R33" s="181"/>
+      <c r="S33" s="181"/>
+      <c r="T33" s="181"/>
+      <c r="U33" s="181"/>
+      <c r="V33" s="182"/>
     </row>
     <row r="34" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="201"/>
-      <c r="C34" s="136" t="s">
+      <c r="B34" s="291"/>
+      <c r="C34" s="189" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="137"/>
-      <c r="E34" s="256">
+      <c r="D34" s="282"/>
+      <c r="E34" s="187">
         <v>20</v>
       </c>
-      <c r="F34" s="125"/>
+      <c r="F34" s="161"/>
       <c r="G34" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="254" t="s">
+      <c r="H34" s="185" t="s">
         <v>3</v>
       </c>
-      <c r="I34" s="255"/>
-      <c r="J34" s="257">
+      <c r="I34" s="186"/>
+      <c r="J34" s="188">
         <v>147.5</v>
       </c>
-      <c r="K34" s="257"/>
+      <c r="K34" s="188"/>
       <c r="L34" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="M34" s="136" t="s">
+      <c r="M34" s="189" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="255"/>
-      <c r="O34" s="256">
+      <c r="N34" s="186"/>
+      <c r="O34" s="187">
         <v>20</v>
       </c>
-      <c r="P34" s="125"/>
+      <c r="P34" s="161"/>
       <c r="Q34" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="R34" s="254" t="s">
+      <c r="R34" s="185" t="s">
         <v>3</v>
       </c>
-      <c r="S34" s="255"/>
-      <c r="T34" s="257">
+      <c r="S34" s="186"/>
+      <c r="T34" s="188">
         <v>147.5</v>
       </c>
-      <c r="U34" s="257"/>
+      <c r="U34" s="188"/>
       <c r="V34" s="32" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="201"/>
-      <c r="C35" s="246" t="s">
+      <c r="B35" s="291"/>
+      <c r="C35" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="247"/>
-      <c r="E35" s="248">
+      <c r="D35" s="148"/>
+      <c r="E35" s="301">
         <v>31.25</v>
       </c>
-      <c r="F35" s="249"/>
+      <c r="F35" s="302"/>
       <c r="G35" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="250" t="s">
+      <c r="H35" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="I35" s="251"/>
-      <c r="J35" s="252">
+      <c r="I35" s="132"/>
+      <c r="J35" s="133">
         <v>10</v>
       </c>
-      <c r="K35" s="252"/>
+      <c r="K35" s="133"/>
       <c r="L35" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="M35" s="246" t="s">
+      <c r="M35" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="N35" s="251"/>
-      <c r="O35" s="248">
+      <c r="N35" s="132"/>
+      <c r="O35" s="301">
         <v>31.25</v>
       </c>
-      <c r="P35" s="249"/>
+      <c r="P35" s="302"/>
       <c r="Q35" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="R35" s="250" t="s">
+      <c r="R35" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="S35" s="251"/>
-      <c r="T35" s="252">
+      <c r="S35" s="132"/>
+      <c r="T35" s="133">
         <v>10</v>
       </c>
-      <c r="U35" s="252"/>
+      <c r="U35" s="133"/>
       <c r="V35" s="34" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="2:22" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="201"/>
-      <c r="C36" s="261" t="s">
+      <c r="B36" s="291"/>
+      <c r="C36" s="135" t="s">
         <v>83</v>
       </c>
-      <c r="D36" s="262"/>
-      <c r="E36" s="266">
+      <c r="D36" s="165"/>
+      <c r="E36" s="303">
         <v>0</v>
       </c>
-      <c r="F36" s="267"/>
-      <c r="G36" s="65" t="s">
+      <c r="F36" s="304"/>
+      <c r="G36" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="H36" s="258" t="s">
+      <c r="H36" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="I36" s="259"/>
-      <c r="J36" s="260">
+      <c r="I36" s="123"/>
+      <c r="J36" s="124">
         <v>8</v>
       </c>
-      <c r="K36" s="260"/>
-      <c r="L36" s="98" t="s">
+      <c r="K36" s="124"/>
+      <c r="L36" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="M36" s="261" t="s">
+      <c r="M36" s="135" t="s">
         <v>83</v>
       </c>
-      <c r="N36" s="262"/>
-      <c r="O36" s="266">
+      <c r="N36" s="165"/>
+      <c r="O36" s="303">
         <v>0</v>
       </c>
-      <c r="P36" s="267"/>
-      <c r="Q36" s="65" t="s">
+      <c r="P36" s="304"/>
+      <c r="Q36" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="R36" s="258" t="s">
+      <c r="R36" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="S36" s="259"/>
-      <c r="T36" s="260">
+      <c r="S36" s="123"/>
+      <c r="T36" s="124">
         <v>8</v>
       </c>
-      <c r="U36" s="260"/>
-      <c r="V36" s="98" t="s">
+      <c r="U36" s="124"/>
+      <c r="V36" s="95" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="201"/>
-      <c r="C37" s="263" t="s">
+      <c r="B37" s="291"/>
+      <c r="C37" s="166" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="128"/>
+      <c r="D37" s="164"/>
       <c r="E37" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="64">
+      <c r="F37" s="63">
         <v>2100</v>
       </c>
       <c r="G37" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="H37" s="63">
+      <c r="H37" s="62">
         <f>IF(J34="","",J34)</f>
         <v>147.5</v>
       </c>
       <c r="I37" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="J37" s="264">
+      <c r="J37" s="139">
         <f>IF(F37=0,"",(F37*H37))</f>
         <v>309750</v>
       </c>
-      <c r="K37" s="264"/>
+      <c r="K37" s="139"/>
       <c r="L37" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="M37" s="263" t="s">
+      <c r="M37" s="166" t="s">
         <v>17</v>
       </c>
-      <c r="N37" s="128"/>
+      <c r="N37" s="164"/>
       <c r="O37" s="40" t="s">
         <v>13</v>
       </c>
@@ -4865,252 +4865,252 @@
       <c r="Q37" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="R37" s="63">
+      <c r="R37" s="62">
         <f>IF(T34="","",T34)</f>
         <v>147.5</v>
       </c>
       <c r="S37" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="T37" s="265">
+      <c r="T37" s="167">
         <f>IF(P37=0,"",(P37*R37))</f>
         <v>280250</v>
       </c>
-      <c r="U37" s="265"/>
+      <c r="U37" s="167"/>
       <c r="V37" s="42" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="201"/>
-      <c r="C38" s="124" t="str">
+      <c r="B38" s="291"/>
+      <c r="C38" s="160" t="str">
         <f>C36</f>
         <v>通常残業</v>
       </c>
-      <c r="D38" s="125"/>
-      <c r="E38" s="130"/>
-      <c r="F38" s="130"/>
+      <c r="D38" s="161"/>
+      <c r="E38" s="151"/>
+      <c r="F38" s="151"/>
       <c r="G38" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="57">
+      <c r="H38" s="298">
         <f>E36</f>
         <v>0</v>
       </c>
       <c r="I38" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="J38" s="264" t="str">
+      <c r="J38" s="139" t="str">
         <f>IF(E38=0,"",(E38*H38))</f>
         <v/>
       </c>
-      <c r="K38" s="264"/>
+      <c r="K38" s="139"/>
       <c r="L38" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="M38" s="124" t="str">
+      <c r="M38" s="160" t="str">
         <f>M36</f>
         <v>通常残業</v>
       </c>
-      <c r="N38" s="125"/>
-      <c r="O38" s="130"/>
-      <c r="P38" s="130"/>
+      <c r="N38" s="161"/>
+      <c r="O38" s="151"/>
+      <c r="P38" s="151"/>
       <c r="Q38" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="R38" s="57">
+      <c r="R38" s="298">
         <f>O36</f>
         <v>0</v>
       </c>
       <c r="S38" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="T38" s="264" t="str">
+      <c r="T38" s="139" t="str">
         <f>IF(O38=0,"",(O38*R38))</f>
         <v/>
       </c>
-      <c r="U38" s="264"/>
+      <c r="U38" s="139"/>
       <c r="V38" s="42" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="39" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="201"/>
-      <c r="C39" s="124" t="str">
+      <c r="B39" s="291"/>
+      <c r="C39" s="160" t="str">
         <f>C35</f>
         <v>深夜時間</v>
       </c>
-      <c r="D39" s="125"/>
-      <c r="E39" s="130">
+      <c r="D39" s="161"/>
+      <c r="E39" s="151">
         <v>525</v>
       </c>
-      <c r="F39" s="130"/>
+      <c r="F39" s="151"/>
       <c r="G39" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="H39" s="96">
+      <c r="H39" s="299">
         <v>31.25</v>
       </c>
       <c r="I39" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="J39" s="264">
+      <c r="J39" s="139">
         <f>IF(E39=0,"",(E39*H39))</f>
         <v>16406.25</v>
       </c>
-      <c r="K39" s="264"/>
+      <c r="K39" s="139"/>
       <c r="L39" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="M39" s="124" t="str">
+      <c r="M39" s="160" t="str">
         <f>M35</f>
         <v>深夜時間</v>
       </c>
-      <c r="N39" s="125"/>
-      <c r="O39" s="130">
+      <c r="N39" s="161"/>
+      <c r="O39" s="151">
         <f>P37*0.25</f>
         <v>475</v>
       </c>
-      <c r="P39" s="130"/>
+      <c r="P39" s="151"/>
       <c r="Q39" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="R39" s="97">
+      <c r="R39" s="300">
         <f>O35</f>
         <v>31.25</v>
       </c>
       <c r="S39" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="T39" s="264">
+      <c r="T39" s="139">
         <f>IF(O39=0,"",(O39*R39))</f>
         <v>14843.75</v>
       </c>
-      <c r="U39" s="264"/>
+      <c r="U39" s="139"/>
       <c r="V39" s="42" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="40" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="201"/>
-      <c r="C40" s="126" t="str">
+      <c r="B40" s="291"/>
+      <c r="C40" s="162" t="str">
         <f>H35</f>
         <v>残業時間</v>
       </c>
-      <c r="D40" s="127"/>
-      <c r="E40" s="130">
+      <c r="D40" s="163"/>
+      <c r="E40" s="151">
         <f>F37*1.25</f>
         <v>2625</v>
       </c>
-      <c r="F40" s="130"/>
+      <c r="F40" s="151"/>
       <c r="G40" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="H40" s="57">
+      <c r="H40" s="298">
         <f>J35</f>
         <v>10</v>
       </c>
       <c r="I40" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="J40" s="264">
+      <c r="J40" s="139">
         <f>IF(E40=0,"",(E40*H40))</f>
         <v>26250</v>
       </c>
-      <c r="K40" s="264"/>
+      <c r="K40" s="139"/>
       <c r="L40" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="M40" s="126" t="str">
+      <c r="M40" s="162" t="str">
         <f>R35</f>
         <v>残業時間</v>
       </c>
-      <c r="N40" s="127"/>
-      <c r="O40" s="130">
+      <c r="N40" s="163"/>
+      <c r="O40" s="151">
         <f>P37*1.25</f>
         <v>2375</v>
       </c>
-      <c r="P40" s="130"/>
+      <c r="P40" s="151"/>
       <c r="Q40" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="R40" s="57">
+      <c r="R40" s="298">
         <f>T35</f>
         <v>10</v>
       </c>
       <c r="S40" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="T40" s="264">
+      <c r="T40" s="139">
         <f>IF(O40=0,"",(O40*R40))</f>
         <v>23750</v>
       </c>
-      <c r="U40" s="264"/>
+      <c r="U40" s="139"/>
       <c r="V40" s="42" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="41" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="201"/>
-      <c r="C41" s="126" t="str">
+      <c r="B41" s="291"/>
+      <c r="C41" s="162" t="str">
         <f>H36</f>
         <v>休日出勤</v>
       </c>
-      <c r="D41" s="128"/>
-      <c r="E41" s="130">
+      <c r="D41" s="164"/>
+      <c r="E41" s="151">
         <f>F37*1.25</f>
         <v>2625</v>
       </c>
-      <c r="F41" s="130"/>
+      <c r="F41" s="151"/>
       <c r="G41" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="H41" s="57">
+      <c r="H41" s="298">
         <f>J36</f>
         <v>8</v>
       </c>
       <c r="I41" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="J41" s="264">
+      <c r="J41" s="139">
         <f>IF(E41=0,"",(E41*H41))</f>
         <v>21000</v>
       </c>
-      <c r="K41" s="264"/>
+      <c r="K41" s="139"/>
       <c r="L41" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="M41" s="126" t="str">
+      <c r="M41" s="162" t="str">
         <f>R36</f>
         <v>休日出勤</v>
       </c>
-      <c r="N41" s="128"/>
-      <c r="O41" s="130">
+      <c r="N41" s="164"/>
+      <c r="O41" s="151">
         <f>P37*1.25</f>
         <v>2375</v>
       </c>
-      <c r="P41" s="130"/>
+      <c r="P41" s="151"/>
       <c r="Q41" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="R41" s="57">
+      <c r="R41" s="298">
         <f>T36</f>
         <v>8</v>
       </c>
       <c r="S41" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="T41" s="264">
+      <c r="T41" s="139">
         <f>IF(O41=0,"",(O41*R41))</f>
         <v>19000</v>
       </c>
-      <c r="U41" s="264"/>
+      <c r="U41" s="139"/>
       <c r="V41" s="42" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="42" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="201"/>
+      <c r="B42" s="291"/>
       <c r="C42" s="36"/>
       <c r="D42" s="43"/>
       <c r="E42" s="7"/>
@@ -5118,34 +5118,34 @@
       <c r="G42" s="38"/>
       <c r="H42" s="37"/>
       <c r="I42" s="38"/>
-      <c r="J42" s="264"/>
-      <c r="K42" s="264"/>
+      <c r="J42" s="139"/>
+      <c r="K42" s="139"/>
       <c r="L42" s="39" t="s">
         <v>16</v>
       </c>
       <c r="M42" s="36"/>
       <c r="N42" s="43"/>
       <c r="O42" s="7"/>
-      <c r="P42" s="282"/>
-      <c r="Q42" s="282"/>
-      <c r="R42" s="282"/>
-      <c r="S42" s="282"/>
-      <c r="T42" s="264"/>
-      <c r="U42" s="264"/>
+      <c r="P42" s="140"/>
+      <c r="Q42" s="140"/>
+      <c r="R42" s="140"/>
+      <c r="S42" s="140"/>
+      <c r="T42" s="139"/>
+      <c r="U42" s="139"/>
       <c r="V42" s="42" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="43" spans="2:22" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="201"/>
-      <c r="C43" s="102" t="s">
+      <c r="B43" s="291"/>
+      <c r="C43" s="294" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="103"/>
-      <c r="E43" s="107" t="s">
+      <c r="D43" s="295"/>
+      <c r="E43" s="296" t="s">
         <v>112</v>
       </c>
-      <c r="F43" s="107"/>
+      <c r="F43" s="296"/>
       <c r="G43" s="46" t="s">
         <v>14</v>
       </c>
@@ -5153,17 +5153,17 @@
       <c r="I43" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="J43" s="270">
+      <c r="J43" s="141">
         <v>13700</v>
       </c>
-      <c r="K43" s="270"/>
+      <c r="K43" s="141"/>
       <c r="L43" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="M43" s="102" t="s">
+      <c r="M43" s="294" t="s">
         <v>56</v>
       </c>
-      <c r="N43" s="103"/>
+      <c r="N43" s="295"/>
       <c r="O43" s="44"/>
       <c r="P43" s="45"/>
       <c r="Q43" s="46" t="s">
@@ -5176,270 +5176,270 @@
       <c r="S43" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="T43" s="270">
+      <c r="T43" s="141">
         <f>IF(P43*R43&gt;=13000,13000,P43*R43)</f>
         <v>0</v>
       </c>
-      <c r="U43" s="270"/>
+      <c r="U43" s="141"/>
       <c r="V43" s="48" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="2:22" s="82" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="202"/>
-      <c r="C44" s="77"/>
-      <c r="D44" s="78"/>
-      <c r="E44" s="79" t="s">
+    <row r="44" spans="2:22" s="81" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="292"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="F44" s="79"/>
-      <c r="G44" s="79"/>
-      <c r="H44" s="80" t="s">
+      <c r="F44" s="78"/>
+      <c r="G44" s="78"/>
+      <c r="H44" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="I44" s="106">
+      <c r="I44" s="289">
         <f>SUM(J37:K43)</f>
         <v>387106.25</v>
       </c>
-      <c r="J44" s="106"/>
-      <c r="K44" s="106"/>
-      <c r="L44" s="81" t="s">
+      <c r="J44" s="289"/>
+      <c r="K44" s="289"/>
+      <c r="L44" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="M44" s="77"/>
-      <c r="N44" s="78"/>
-      <c r="O44" s="79" t="s">
+      <c r="M44" s="76"/>
+      <c r="N44" s="77"/>
+      <c r="O44" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="P44" s="79"/>
-      <c r="Q44" s="79"/>
-      <c r="R44" s="80" t="s">
+      <c r="P44" s="78"/>
+      <c r="Q44" s="78"/>
+      <c r="R44" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="S44" s="106">
+      <c r="S44" s="289">
         <f>SUM(T37:U43)</f>
         <v>337843.75</v>
       </c>
-      <c r="T44" s="106"/>
-      <c r="U44" s="106"/>
-      <c r="V44" s="81" t="s">
+      <c r="T44" s="289"/>
+      <c r="U44" s="289"/>
+      <c r="V44" s="80" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="45" spans="2:22" s="2" customFormat="1" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="138"/>
-      <c r="C45" s="138"/>
-      <c r="D45" s="138"/>
-      <c r="E45" s="138"/>
-      <c r="F45" s="138"/>
-      <c r="G45" s="138"/>
-      <c r="H45" s="138"/>
-      <c r="I45" s="138"/>
-      <c r="J45" s="138"/>
-      <c r="K45" s="138"/>
-      <c r="L45" s="138"/>
-      <c r="M45" s="138"/>
-      <c r="N45" s="138"/>
-      <c r="O45" s="138"/>
-      <c r="P45" s="138"/>
-      <c r="Q45" s="138"/>
-      <c r="R45" s="138"/>
-      <c r="S45" s="138"/>
-      <c r="T45" s="138"/>
-      <c r="U45" s="138"/>
-      <c r="V45" s="138"/>
+      <c r="B45" s="125"/>
+      <c r="C45" s="125"/>
+      <c r="D45" s="125"/>
+      <c r="E45" s="125"/>
+      <c r="F45" s="125"/>
+      <c r="G45" s="125"/>
+      <c r="H45" s="125"/>
+      <c r="I45" s="125"/>
+      <c r="J45" s="125"/>
+      <c r="K45" s="125"/>
+      <c r="L45" s="125"/>
+      <c r="M45" s="125"/>
+      <c r="N45" s="125"/>
+      <c r="O45" s="125"/>
+      <c r="P45" s="125"/>
+      <c r="Q45" s="125"/>
+      <c r="R45" s="125"/>
+      <c r="S45" s="125"/>
+      <c r="T45" s="125"/>
+      <c r="U45" s="125"/>
+      <c r="V45" s="125"/>
     </row>
     <row r="46" spans="2:22" s="2" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="139" t="s">
+      <c r="B46" s="283" t="s">
         <v>48</v>
       </c>
-      <c r="C46" s="274" t="s">
+      <c r="C46" s="142" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="275"/>
-      <c r="E46" s="273">
+      <c r="D46" s="143"/>
+      <c r="E46" s="145">
         <f>E40</f>
         <v>2625</v>
       </c>
-      <c r="F46" s="271"/>
+      <c r="F46" s="146"/>
       <c r="G46" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="H46" s="276" t="s">
+      <c r="H46" s="149" t="s">
         <v>26</v>
       </c>
-      <c r="I46" s="277"/>
-      <c r="J46" s="271">
+      <c r="I46" s="150"/>
+      <c r="J46" s="146">
         <f>E39</f>
         <v>525</v>
       </c>
-      <c r="K46" s="271"/>
+      <c r="K46" s="146"/>
       <c r="L46" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="M46" s="274" t="s">
+      <c r="M46" s="142" t="s">
         <v>25</v>
       </c>
-      <c r="N46" s="275"/>
-      <c r="O46" s="273">
+      <c r="N46" s="143"/>
+      <c r="O46" s="145">
         <f>O40</f>
         <v>2375</v>
       </c>
-      <c r="P46" s="271"/>
+      <c r="P46" s="146"/>
       <c r="Q46" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="R46" s="276" t="s">
+      <c r="R46" s="149" t="s">
         <v>26</v>
       </c>
-      <c r="S46" s="277"/>
-      <c r="T46" s="271">
+      <c r="S46" s="150"/>
+      <c r="T46" s="146">
         <f>O39</f>
         <v>475</v>
       </c>
-      <c r="U46" s="271"/>
+      <c r="U46" s="146"/>
       <c r="V46" s="50" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="47" spans="2:22" s="2" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="140"/>
-      <c r="C47" s="246" t="s">
+      <c r="B47" s="284"/>
+      <c r="C47" s="147" t="s">
         <v>28</v>
       </c>
-      <c r="D47" s="247"/>
-      <c r="E47" s="272">
+      <c r="D47" s="148"/>
+      <c r="E47" s="144">
         <f>E41</f>
         <v>2625</v>
       </c>
-      <c r="F47" s="252"/>
+      <c r="F47" s="133"/>
       <c r="G47" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="H47" s="250" t="s">
+      <c r="H47" s="131" t="s">
         <v>83</v>
       </c>
-      <c r="I47" s="251"/>
-      <c r="J47" s="252">
+      <c r="I47" s="132"/>
+      <c r="J47" s="133">
         <f>F39</f>
         <v>0</v>
       </c>
-      <c r="K47" s="252"/>
+      <c r="K47" s="133"/>
       <c r="L47" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="M47" s="246" t="s">
+      <c r="M47" s="147" t="s">
         <v>28</v>
       </c>
-      <c r="N47" s="247"/>
-      <c r="O47" s="272">
+      <c r="N47" s="148"/>
+      <c r="O47" s="144">
         <f>O41</f>
         <v>2375</v>
       </c>
-      <c r="P47" s="252"/>
+      <c r="P47" s="133"/>
       <c r="Q47" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="R47" s="250" t="s">
+      <c r="R47" s="131" t="s">
         <v>83</v>
       </c>
-      <c r="S47" s="251"/>
-      <c r="T47" s="252">
+      <c r="S47" s="132"/>
+      <c r="T47" s="133">
         <f>P39</f>
         <v>0</v>
       </c>
-      <c r="U47" s="252"/>
+      <c r="U47" s="133"/>
       <c r="V47" s="34" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="48" spans="2:22" s="2" customFormat="1" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="140"/>
-      <c r="C48" s="280"/>
-      <c r="D48" s="281"/>
-      <c r="E48" s="272"/>
-      <c r="F48" s="252"/>
+      <c r="B48" s="284"/>
+      <c r="C48" s="137"/>
+      <c r="D48" s="138"/>
+      <c r="E48" s="144"/>
+      <c r="F48" s="133"/>
       <c r="G48" s="33"/>
-      <c r="H48" s="250"/>
-      <c r="I48" s="251"/>
-      <c r="J48" s="252"/>
-      <c r="K48" s="252"/>
+      <c r="H48" s="131"/>
+      <c r="I48" s="132"/>
+      <c r="J48" s="133"/>
+      <c r="K48" s="133"/>
       <c r="L48" s="34"/>
-      <c r="M48" s="280"/>
-      <c r="N48" s="281"/>
-      <c r="O48" s="272"/>
-      <c r="P48" s="252"/>
+      <c r="M48" s="137"/>
+      <c r="N48" s="138"/>
+      <c r="O48" s="144"/>
+      <c r="P48" s="133"/>
       <c r="Q48" s="33"/>
-      <c r="R48" s="250"/>
-      <c r="S48" s="251"/>
-      <c r="T48" s="252"/>
-      <c r="U48" s="252"/>
+      <c r="R48" s="131"/>
+      <c r="S48" s="132"/>
+      <c r="T48" s="133"/>
+      <c r="U48" s="133"/>
       <c r="V48" s="34"/>
     </row>
     <row r="49" spans="2:23" s="2" customFormat="1" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="141"/>
-      <c r="C49" s="278" t="s">
+      <c r="B49" s="285"/>
+      <c r="C49" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="D49" s="261"/>
-      <c r="E49" s="279">
+      <c r="D49" s="135"/>
+      <c r="E49" s="136">
         <v>13000</v>
       </c>
-      <c r="F49" s="260"/>
+      <c r="F49" s="124"/>
       <c r="G49" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="H49" s="258"/>
-      <c r="I49" s="259"/>
-      <c r="J49" s="260"/>
-      <c r="K49" s="260"/>
+      <c r="H49" s="122"/>
+      <c r="I49" s="123"/>
+      <c r="J49" s="124"/>
+      <c r="K49" s="124"/>
       <c r="L49" s="35"/>
-      <c r="M49" s="278" t="s">
+      <c r="M49" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="N49" s="261"/>
-      <c r="O49" s="279">
+      <c r="N49" s="135"/>
+      <c r="O49" s="136">
         <v>1300</v>
       </c>
-      <c r="P49" s="260"/>
+      <c r="P49" s="124"/>
       <c r="Q49" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="R49" s="258"/>
-      <c r="S49" s="259"/>
-      <c r="T49" s="260"/>
-      <c r="U49" s="260"/>
+      <c r="R49" s="122"/>
+      <c r="S49" s="123"/>
+      <c r="T49" s="124"/>
+      <c r="U49" s="124"/>
       <c r="V49" s="35"/>
     </row>
     <row r="50" spans="2:23" s="2" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="138"/>
-      <c r="C50" s="138"/>
-      <c r="D50" s="138"/>
-      <c r="E50" s="138"/>
-      <c r="F50" s="138"/>
-      <c r="G50" s="138"/>
-      <c r="H50" s="138"/>
-      <c r="I50" s="138"/>
-      <c r="J50" s="138"/>
-      <c r="K50" s="138"/>
-      <c r="L50" s="138"/>
-      <c r="M50" s="138"/>
-      <c r="N50" s="138"/>
-      <c r="O50" s="138"/>
-      <c r="P50" s="138"/>
-      <c r="Q50" s="138"/>
-      <c r="R50" s="138"/>
-      <c r="S50" s="138"/>
-      <c r="T50" s="138"/>
-      <c r="U50" s="138"/>
-      <c r="V50" s="138"/>
+      <c r="B50" s="125"/>
+      <c r="C50" s="125"/>
+      <c r="D50" s="125"/>
+      <c r="E50" s="125"/>
+      <c r="F50" s="125"/>
+      <c r="G50" s="125"/>
+      <c r="H50" s="125"/>
+      <c r="I50" s="125"/>
+      <c r="J50" s="125"/>
+      <c r="K50" s="125"/>
+      <c r="L50" s="125"/>
+      <c r="M50" s="125"/>
+      <c r="N50" s="125"/>
+      <c r="O50" s="125"/>
+      <c r="P50" s="125"/>
+      <c r="Q50" s="125"/>
+      <c r="R50" s="125"/>
+      <c r="S50" s="125"/>
+      <c r="T50" s="125"/>
+      <c r="U50" s="125"/>
+      <c r="V50" s="125"/>
     </row>
     <row r="51" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="185" t="s">
+      <c r="B51" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="297"/>
-      <c r="D51" s="186"/>
+      <c r="C51" s="127"/>
+      <c r="D51" s="128"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
         <v>35</v>
@@ -5472,669 +5472,669 @@
       <c r="V51" s="9"/>
     </row>
     <row r="52" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="185" t="s">
+      <c r="B52" s="126" t="s">
         <v>75</v>
       </c>
-      <c r="C52" s="297"/>
-      <c r="D52" s="186"/>
-      <c r="E52" s="298" t="s">
+      <c r="C52" s="127"/>
+      <c r="D52" s="128"/>
+      <c r="E52" s="129" t="s">
         <v>77</v>
       </c>
-      <c r="F52" s="287"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="299" t="s">
+      <c r="F52" s="111"/>
+      <c r="G52" s="82"/>
+      <c r="H52" s="130" t="s">
         <v>78</v>
       </c>
-      <c r="I52" s="287"/>
-      <c r="J52" s="85"/>
-      <c r="K52" s="287" t="s">
+      <c r="I52" s="111"/>
+      <c r="J52" s="84"/>
+      <c r="K52" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="L52" s="287"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="299" t="s">
+      <c r="L52" s="111"/>
+      <c r="M52" s="82"/>
+      <c r="N52" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="O52" s="287"/>
-      <c r="P52" s="85"/>
-      <c r="Q52" s="299" t="s">
+      <c r="O52" s="111"/>
+      <c r="P52" s="84"/>
+      <c r="Q52" s="130" t="s">
         <v>76</v>
       </c>
-      <c r="R52" s="287"/>
-      <c r="S52" s="85"/>
-      <c r="T52" s="287" t="s">
+      <c r="R52" s="111"/>
+      <c r="S52" s="84"/>
+      <c r="T52" s="111" t="s">
         <v>101</v>
       </c>
-      <c r="U52" s="287"/>
-      <c r="V52" s="84"/>
+      <c r="U52" s="111"/>
+      <c r="V52" s="83"/>
       <c r="W52" s="8"/>
     </row>
     <row r="53" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="113" t="s">
+      <c r="B53" s="249" t="s">
         <v>100</v>
       </c>
-      <c r="C53" s="114"/>
-      <c r="D53" s="114"/>
-      <c r="E53" s="150" t="s">
+      <c r="C53" s="256"/>
+      <c r="D53" s="256"/>
+      <c r="E53" s="288" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="151"/>
-      <c r="G53" s="151"/>
-      <c r="H53" s="151" t="s">
+      <c r="F53" s="112"/>
+      <c r="G53" s="112"/>
+      <c r="H53" s="112" t="s">
         <v>63</v>
       </c>
-      <c r="I53" s="151"/>
-      <c r="J53" s="86"/>
-      <c r="K53" s="151" t="s">
+      <c r="I53" s="112"/>
+      <c r="J53" s="85"/>
+      <c r="K53" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="L53" s="151"/>
-      <c r="M53" s="87"/>
-      <c r="N53" s="148" t="s">
+      <c r="L53" s="112"/>
+      <c r="M53" s="86"/>
+      <c r="N53" s="286" t="s">
         <v>144</v>
       </c>
-      <c r="O53" s="148"/>
-      <c r="P53" s="148"/>
-      <c r="Q53" s="148"/>
-      <c r="R53" s="148"/>
-      <c r="S53" s="148"/>
-      <c r="T53" s="148"/>
-      <c r="U53" s="148"/>
-      <c r="V53" s="149"/>
+      <c r="O53" s="286"/>
+      <c r="P53" s="286"/>
+      <c r="Q53" s="286"/>
+      <c r="R53" s="286"/>
+      <c r="S53" s="286"/>
+      <c r="T53" s="286"/>
+      <c r="U53" s="286"/>
+      <c r="V53" s="287"/>
     </row>
     <row r="54" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="99"/>
-      <c r="C54" s="100"/>
-      <c r="D54" s="100"/>
-      <c r="E54" s="129" t="s">
+      <c r="B54" s="234"/>
+      <c r="C54" s="293"/>
+      <c r="D54" s="293"/>
+      <c r="E54" s="297" t="s">
         <v>103</v>
       </c>
-      <c r="F54" s="121"/>
-      <c r="G54" s="121"/>
-      <c r="H54" s="121" t="s">
+      <c r="F54" s="280"/>
+      <c r="G54" s="280"/>
+      <c r="H54" s="280" t="s">
         <v>63</v>
       </c>
-      <c r="I54" s="121"/>
-      <c r="J54" s="88"/>
-      <c r="K54" s="121" t="s">
+      <c r="I54" s="280"/>
+      <c r="J54" s="87"/>
+      <c r="K54" s="280" t="s">
         <v>64</v>
       </c>
-      <c r="L54" s="121"/>
-      <c r="M54" s="89"/>
-      <c r="N54" s="104"/>
-      <c r="O54" s="104"/>
-      <c r="P54" s="104"/>
-      <c r="Q54" s="104"/>
-      <c r="R54" s="104"/>
-      <c r="S54" s="104"/>
-      <c r="T54" s="104"/>
-      <c r="U54" s="104"/>
-      <c r="V54" s="105"/>
+      <c r="L54" s="280"/>
+      <c r="M54" s="88"/>
+      <c r="N54" s="154"/>
+      <c r="O54" s="154"/>
+      <c r="P54" s="154"/>
+      <c r="Q54" s="154"/>
+      <c r="R54" s="154"/>
+      <c r="S54" s="154"/>
+      <c r="T54" s="154"/>
+      <c r="U54" s="154"/>
+      <c r="V54" s="155"/>
     </row>
     <row r="55" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="99"/>
-      <c r="C55" s="100"/>
-      <c r="D55" s="100"/>
-      <c r="E55" s="129" t="s">
+      <c r="B55" s="234"/>
+      <c r="C55" s="293"/>
+      <c r="D55" s="293"/>
+      <c r="E55" s="297" t="s">
         <v>122</v>
       </c>
-      <c r="F55" s="121"/>
-      <c r="G55" s="121"/>
-      <c r="H55" s="121" t="s">
+      <c r="F55" s="280"/>
+      <c r="G55" s="280"/>
+      <c r="H55" s="280" t="s">
         <v>63</v>
       </c>
-      <c r="I55" s="121"/>
-      <c r="J55" s="88"/>
-      <c r="K55" s="121" t="s">
+      <c r="I55" s="280"/>
+      <c r="J55" s="87"/>
+      <c r="K55" s="280" t="s">
         <v>64</v>
       </c>
-      <c r="L55" s="121"/>
-      <c r="M55" s="89"/>
-      <c r="N55" s="104"/>
-      <c r="O55" s="104"/>
-      <c r="P55" s="104"/>
-      <c r="Q55" s="104"/>
-      <c r="R55" s="104"/>
-      <c r="S55" s="104"/>
-      <c r="T55" s="104"/>
-      <c r="U55" s="104"/>
-      <c r="V55" s="105"/>
+      <c r="L55" s="280"/>
+      <c r="M55" s="88"/>
+      <c r="N55" s="154"/>
+      <c r="O55" s="154"/>
+      <c r="P55" s="154"/>
+      <c r="Q55" s="154"/>
+      <c r="R55" s="154"/>
+      <c r="S55" s="154"/>
+      <c r="T55" s="154"/>
+      <c r="U55" s="154"/>
+      <c r="V55" s="155"/>
     </row>
     <row r="56" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="116"/>
-      <c r="C56" s="117"/>
-      <c r="D56" s="117"/>
-      <c r="E56" s="123" t="s">
+      <c r="B56" s="224"/>
+      <c r="C56" s="257"/>
+      <c r="D56" s="257"/>
+      <c r="E56" s="158" t="s">
         <v>101</v>
       </c>
-      <c r="F56" s="122"/>
-      <c r="G56" s="122"/>
-      <c r="H56" s="122" t="s">
+      <c r="F56" s="159"/>
+      <c r="G56" s="159"/>
+      <c r="H56" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="I56" s="122"/>
-      <c r="J56" s="90"/>
-      <c r="K56" s="122" t="s">
+      <c r="I56" s="159"/>
+      <c r="J56" s="89"/>
+      <c r="K56" s="159" t="s">
         <v>64</v>
       </c>
-      <c r="L56" s="122"/>
-      <c r="M56" s="91"/>
-      <c r="N56" s="268" t="s">
+      <c r="L56" s="159"/>
+      <c r="M56" s="90"/>
+      <c r="N56" s="156" t="s">
         <v>143</v>
       </c>
-      <c r="O56" s="268"/>
-      <c r="P56" s="268"/>
-      <c r="Q56" s="268"/>
-      <c r="R56" s="268"/>
-      <c r="S56" s="268"/>
-      <c r="T56" s="268"/>
-      <c r="U56" s="268"/>
-      <c r="V56" s="269"/>
+      <c r="O56" s="156"/>
+      <c r="P56" s="156"/>
+      <c r="Q56" s="156"/>
+      <c r="R56" s="156"/>
+      <c r="S56" s="156"/>
+      <c r="T56" s="156"/>
+      <c r="U56" s="156"/>
+      <c r="V56" s="157"/>
     </row>
     <row r="57" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="70"/>
-      <c r="C57" s="72" t="s">
+      <c r="B57" s="69"/>
+      <c r="C57" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="D57" s="71"/>
-      <c r="E57" s="123" t="s">
+      <c r="D57" s="70"/>
+      <c r="E57" s="158" t="s">
         <v>107</v>
       </c>
-      <c r="F57" s="122"/>
-      <c r="G57" s="122"/>
-      <c r="H57" s="122" t="s">
+      <c r="F57" s="159"/>
+      <c r="G57" s="159"/>
+      <c r="H57" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="I57" s="122"/>
-      <c r="J57" s="88"/>
-      <c r="K57" s="122" t="s">
+      <c r="I57" s="159"/>
+      <c r="J57" s="87"/>
+      <c r="K57" s="159" t="s">
         <v>64</v>
       </c>
-      <c r="L57" s="122"/>
-      <c r="M57" s="89"/>
-      <c r="N57" s="90" t="s">
+      <c r="L57" s="159"/>
+      <c r="M57" s="88"/>
+      <c r="N57" s="89" t="s">
         <v>108</v>
       </c>
-      <c r="O57" s="90"/>
-      <c r="P57" s="90"/>
-      <c r="Q57" s="90"/>
-      <c r="R57" s="90"/>
-      <c r="S57" s="90"/>
-      <c r="T57" s="90"/>
-      <c r="U57" s="90"/>
-      <c r="V57" s="92"/>
+      <c r="O57" s="89"/>
+      <c r="P57" s="89"/>
+      <c r="Q57" s="89"/>
+      <c r="R57" s="89"/>
+      <c r="S57" s="89"/>
+      <c r="T57" s="89"/>
+      <c r="U57" s="89"/>
+      <c r="V57" s="91"/>
     </row>
     <row r="58" spans="2:23" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="113" t="s">
+      <c r="B58" s="249" t="s">
         <v>39</v>
       </c>
-      <c r="C58" s="114"/>
-      <c r="D58" s="115"/>
-      <c r="E58" s="288" t="s">
+      <c r="C58" s="256"/>
+      <c r="D58" s="250"/>
+      <c r="E58" s="113" t="s">
         <v>110</v>
       </c>
-      <c r="F58" s="289"/>
-      <c r="G58" s="289"/>
-      <c r="H58" s="289"/>
-      <c r="I58" s="289"/>
-      <c r="J58" s="289"/>
-      <c r="K58" s="289"/>
-      <c r="L58" s="289"/>
-      <c r="M58" s="289"/>
-      <c r="N58" s="289"/>
-      <c r="O58" s="289"/>
-      <c r="P58" s="289"/>
-      <c r="Q58" s="289"/>
-      <c r="R58" s="289"/>
-      <c r="S58" s="289"/>
-      <c r="T58" s="289"/>
-      <c r="U58" s="289"/>
-      <c r="V58" s="290"/>
+      <c r="F58" s="114"/>
+      <c r="G58" s="114"/>
+      <c r="H58" s="114"/>
+      <c r="I58" s="114"/>
+      <c r="J58" s="114"/>
+      <c r="K58" s="114"/>
+      <c r="L58" s="114"/>
+      <c r="M58" s="114"/>
+      <c r="N58" s="114"/>
+      <c r="O58" s="114"/>
+      <c r="P58" s="114"/>
+      <c r="Q58" s="114"/>
+      <c r="R58" s="114"/>
+      <c r="S58" s="114"/>
+      <c r="T58" s="114"/>
+      <c r="U58" s="114"/>
+      <c r="V58" s="115"/>
     </row>
     <row r="59" spans="2:23" s="2" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="116"/>
-      <c r="C59" s="117"/>
-      <c r="D59" s="118"/>
-      <c r="E59" s="291"/>
-      <c r="F59" s="292"/>
-      <c r="G59" s="292"/>
-      <c r="H59" s="292"/>
-      <c r="I59" s="292"/>
-      <c r="J59" s="292"/>
-      <c r="K59" s="292"/>
-      <c r="L59" s="292"/>
-      <c r="M59" s="292"/>
-      <c r="N59" s="292"/>
-      <c r="O59" s="292"/>
-      <c r="P59" s="292"/>
-      <c r="Q59" s="292"/>
-      <c r="R59" s="292"/>
-      <c r="S59" s="292"/>
-      <c r="T59" s="292"/>
-      <c r="U59" s="292"/>
-      <c r="V59" s="293"/>
+      <c r="B59" s="224"/>
+      <c r="C59" s="257"/>
+      <c r="D59" s="225"/>
+      <c r="E59" s="116"/>
+      <c r="F59" s="117"/>
+      <c r="G59" s="117"/>
+      <c r="H59" s="117"/>
+      <c r="I59" s="117"/>
+      <c r="J59" s="117"/>
+      <c r="K59" s="117"/>
+      <c r="L59" s="117"/>
+      <c r="M59" s="117"/>
+      <c r="N59" s="117"/>
+      <c r="O59" s="117"/>
+      <c r="P59" s="117"/>
+      <c r="Q59" s="117"/>
+      <c r="R59" s="117"/>
+      <c r="S59" s="117"/>
+      <c r="T59" s="117"/>
+      <c r="U59" s="117"/>
+      <c r="V59" s="118"/>
     </row>
     <row r="60" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="73"/>
-      <c r="C60" s="74"/>
-      <c r="D60" s="75"/>
-      <c r="E60" s="119" t="s">
+      <c r="B60" s="72"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="74"/>
+      <c r="E60" s="272" t="s">
         <v>109</v>
       </c>
-      <c r="F60" s="119"/>
-      <c r="G60" s="119"/>
-      <c r="H60" s="119"/>
-      <c r="I60" s="119"/>
-      <c r="J60" s="119"/>
-      <c r="K60" s="119"/>
-      <c r="L60" s="119"/>
-      <c r="M60" s="119"/>
-      <c r="N60" s="119"/>
-      <c r="O60" s="119"/>
-      <c r="P60" s="119"/>
-      <c r="Q60" s="119"/>
-      <c r="R60" s="119"/>
-      <c r="S60" s="119"/>
-      <c r="T60" s="119"/>
-      <c r="U60" s="119"/>
-      <c r="V60" s="120"/>
+      <c r="F60" s="272"/>
+      <c r="G60" s="272"/>
+      <c r="H60" s="272"/>
+      <c r="I60" s="272"/>
+      <c r="J60" s="272"/>
+      <c r="K60" s="272"/>
+      <c r="L60" s="272"/>
+      <c r="M60" s="272"/>
+      <c r="N60" s="272"/>
+      <c r="O60" s="272"/>
+      <c r="P60" s="272"/>
+      <c r="Q60" s="272"/>
+      <c r="R60" s="272"/>
+      <c r="S60" s="272"/>
+      <c r="T60" s="272"/>
+      <c r="U60" s="272"/>
+      <c r="V60" s="273"/>
     </row>
     <row r="61" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="99" t="s">
+      <c r="B61" s="234" t="s">
         <v>90</v>
       </c>
-      <c r="C61" s="100"/>
-      <c r="D61" s="101"/>
-      <c r="E61" s="154" t="s">
+      <c r="C61" s="293"/>
+      <c r="D61" s="235"/>
+      <c r="E61" s="152" t="s">
         <v>99</v>
       </c>
-      <c r="F61" s="154"/>
-      <c r="G61" s="154"/>
-      <c r="H61" s="154"/>
-      <c r="I61" s="154"/>
-      <c r="J61" s="154"/>
-      <c r="K61" s="154"/>
-      <c r="L61" s="154"/>
-      <c r="M61" s="154"/>
-      <c r="N61" s="154"/>
-      <c r="O61" s="154"/>
-      <c r="P61" s="154"/>
-      <c r="Q61" s="154"/>
-      <c r="R61" s="154"/>
-      <c r="S61" s="154"/>
-      <c r="T61" s="154"/>
-      <c r="U61" s="154"/>
-      <c r="V61" s="155"/>
+      <c r="F61" s="152"/>
+      <c r="G61" s="152"/>
+      <c r="H61" s="152"/>
+      <c r="I61" s="152"/>
+      <c r="J61" s="152"/>
+      <c r="K61" s="152"/>
+      <c r="L61" s="152"/>
+      <c r="M61" s="152"/>
+      <c r="N61" s="152"/>
+      <c r="O61" s="152"/>
+      <c r="P61" s="152"/>
+      <c r="Q61" s="152"/>
+      <c r="R61" s="152"/>
+      <c r="S61" s="152"/>
+      <c r="T61" s="152"/>
+      <c r="U61" s="152"/>
+      <c r="V61" s="153"/>
     </row>
     <row r="62" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="70"/>
-      <c r="C62" s="72" t="s">
+      <c r="B62" s="69"/>
+      <c r="C62" s="71" t="s">
         <v>94</v>
       </c>
-      <c r="D62" s="71"/>
-      <c r="E62" s="154" t="s">
+      <c r="D62" s="70"/>
+      <c r="E62" s="152" t="s">
         <v>98</v>
       </c>
-      <c r="F62" s="154"/>
-      <c r="G62" s="154"/>
-      <c r="H62" s="154"/>
-      <c r="I62" s="154"/>
-      <c r="J62" s="154"/>
-      <c r="K62" s="154"/>
-      <c r="L62" s="154"/>
-      <c r="M62" s="154"/>
-      <c r="N62" s="154"/>
-      <c r="O62" s="154"/>
-      <c r="P62" s="154"/>
-      <c r="Q62" s="154"/>
-      <c r="R62" s="154"/>
-      <c r="S62" s="154"/>
-      <c r="T62" s="154"/>
-      <c r="U62" s="154"/>
-      <c r="V62" s="155"/>
+      <c r="F62" s="152"/>
+      <c r="G62" s="152"/>
+      <c r="H62" s="152"/>
+      <c r="I62" s="152"/>
+      <c r="J62" s="152"/>
+      <c r="K62" s="152"/>
+      <c r="L62" s="152"/>
+      <c r="M62" s="152"/>
+      <c r="N62" s="152"/>
+      <c r="O62" s="152"/>
+      <c r="P62" s="152"/>
+      <c r="Q62" s="152"/>
+      <c r="R62" s="152"/>
+      <c r="S62" s="152"/>
+      <c r="T62" s="152"/>
+      <c r="U62" s="152"/>
+      <c r="V62" s="153"/>
     </row>
     <row r="63" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="70"/>
-      <c r="C63" s="72" t="s">
+      <c r="B63" s="69"/>
+      <c r="C63" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="D63" s="71"/>
-      <c r="E63" s="156" t="s">
+      <c r="D63" s="70"/>
+      <c r="E63" s="276" t="s">
         <v>92</v>
       </c>
-      <c r="F63" s="156"/>
-      <c r="G63" s="156" t="str">
+      <c r="F63" s="276"/>
+      <c r="G63" s="276" t="str">
         <f>D3</f>
         <v>富双合成株式会社　</v>
       </c>
-      <c r="H63" s="156"/>
-      <c r="I63" s="156"/>
-      <c r="J63" s="156"/>
-      <c r="K63" s="156"/>
-      <c r="L63" s="156" t="str">
+      <c r="H63" s="276"/>
+      <c r="I63" s="276"/>
+      <c r="J63" s="276"/>
+      <c r="K63" s="276"/>
+      <c r="L63" s="276" t="str">
         <f>J3</f>
         <v>久喜工場</v>
       </c>
-      <c r="M63" s="156"/>
-      <c r="N63" s="156"/>
-      <c r="O63" s="156"/>
-      <c r="P63" s="154" t="s">
+      <c r="M63" s="276"/>
+      <c r="N63" s="276"/>
+      <c r="O63" s="276"/>
+      <c r="P63" s="152" t="s">
         <v>93</v>
       </c>
-      <c r="Q63" s="154"/>
-      <c r="R63" s="154"/>
-      <c r="S63" s="154"/>
-      <c r="T63" s="154"/>
-      <c r="U63" s="154"/>
-      <c r="V63" s="155"/>
+      <c r="Q63" s="152"/>
+      <c r="R63" s="152"/>
+      <c r="S63" s="152"/>
+      <c r="T63" s="152"/>
+      <c r="U63" s="152"/>
+      <c r="V63" s="153"/>
     </row>
     <row r="64" spans="2:23" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="67"/>
-      <c r="C64" s="68"/>
-      <c r="D64" s="69"/>
-      <c r="E64" s="159" t="s">
+      <c r="B64" s="66"/>
+      <c r="C64" s="67"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="279" t="s">
         <v>95</v>
       </c>
-      <c r="F64" s="157"/>
-      <c r="G64" s="157"/>
-      <c r="H64" s="157"/>
-      <c r="I64" s="157"/>
-      <c r="J64" s="157"/>
-      <c r="K64" s="157"/>
-      <c r="L64" s="157"/>
-      <c r="M64" s="157" t="s">
+      <c r="F64" s="277"/>
+      <c r="G64" s="277"/>
+      <c r="H64" s="277"/>
+      <c r="I64" s="277"/>
+      <c r="J64" s="277"/>
+      <c r="K64" s="277"/>
+      <c r="L64" s="277"/>
+      <c r="M64" s="277" t="s">
         <v>96</v>
       </c>
-      <c r="N64" s="157"/>
-      <c r="O64" s="157"/>
-      <c r="P64" s="157"/>
-      <c r="Q64" s="157"/>
-      <c r="R64" s="157"/>
-      <c r="S64" s="157"/>
-      <c r="T64" s="157"/>
-      <c r="U64" s="157"/>
-      <c r="V64" s="158"/>
+      <c r="N64" s="277"/>
+      <c r="O64" s="277"/>
+      <c r="P64" s="277"/>
+      <c r="Q64" s="277"/>
+      <c r="R64" s="277"/>
+      <c r="S64" s="277"/>
+      <c r="T64" s="277"/>
+      <c r="U64" s="277"/>
+      <c r="V64" s="278"/>
     </row>
     <row r="65" spans="2:22" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="113" t="s">
+      <c r="B65" s="249" t="s">
         <v>104</v>
       </c>
-      <c r="C65" s="114"/>
-      <c r="D65" s="115"/>
-      <c r="E65" s="119" t="s">
+      <c r="C65" s="256"/>
+      <c r="D65" s="250"/>
+      <c r="E65" s="272" t="s">
         <v>113</v>
       </c>
-      <c r="F65" s="119"/>
-      <c r="G65" s="119"/>
-      <c r="H65" s="119"/>
-      <c r="I65" s="119"/>
-      <c r="J65" s="119"/>
-      <c r="K65" s="119"/>
-      <c r="L65" s="119"/>
-      <c r="M65" s="119"/>
-      <c r="N65" s="119"/>
-      <c r="O65" s="119"/>
-      <c r="P65" s="119"/>
-      <c r="Q65" s="119"/>
-      <c r="R65" s="119"/>
-      <c r="S65" s="119"/>
-      <c r="T65" s="119"/>
-      <c r="U65" s="119"/>
-      <c r="V65" s="120"/>
+      <c r="F65" s="272"/>
+      <c r="G65" s="272"/>
+      <c r="H65" s="272"/>
+      <c r="I65" s="272"/>
+      <c r="J65" s="272"/>
+      <c r="K65" s="272"/>
+      <c r="L65" s="272"/>
+      <c r="M65" s="272"/>
+      <c r="N65" s="272"/>
+      <c r="O65" s="272"/>
+      <c r="P65" s="272"/>
+      <c r="Q65" s="272"/>
+      <c r="R65" s="272"/>
+      <c r="S65" s="272"/>
+      <c r="T65" s="272"/>
+      <c r="U65" s="272"/>
+      <c r="V65" s="273"/>
     </row>
     <row r="66" spans="2:22" s="2" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="116" t="s">
+      <c r="B66" s="224" t="s">
         <v>105</v>
       </c>
-      <c r="C66" s="117"/>
-      <c r="D66" s="118"/>
-      <c r="E66" s="152" t="s">
+      <c r="C66" s="257"/>
+      <c r="D66" s="225"/>
+      <c r="E66" s="274" t="s">
         <v>97</v>
       </c>
-      <c r="F66" s="152"/>
-      <c r="G66" s="152"/>
-      <c r="H66" s="152"/>
-      <c r="I66" s="152"/>
-      <c r="J66" s="152"/>
-      <c r="K66" s="152"/>
-      <c r="L66" s="152"/>
-      <c r="M66" s="152"/>
-      <c r="N66" s="152"/>
-      <c r="O66" s="152"/>
-      <c r="P66" s="152"/>
-      <c r="Q66" s="152"/>
-      <c r="R66" s="152"/>
-      <c r="S66" s="152"/>
-      <c r="T66" s="152"/>
-      <c r="U66" s="152"/>
-      <c r="V66" s="153"/>
+      <c r="F66" s="274"/>
+      <c r="G66" s="274"/>
+      <c r="H66" s="274"/>
+      <c r="I66" s="274"/>
+      <c r="J66" s="274"/>
+      <c r="K66" s="274"/>
+      <c r="L66" s="274"/>
+      <c r="M66" s="274"/>
+      <c r="N66" s="274"/>
+      <c r="O66" s="274"/>
+      <c r="P66" s="274"/>
+      <c r="Q66" s="274"/>
+      <c r="R66" s="274"/>
+      <c r="S66" s="274"/>
+      <c r="T66" s="274"/>
+      <c r="U66" s="274"/>
+      <c r="V66" s="275"/>
     </row>
     <row r="67" spans="2:22" s="2" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B67" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C67" s="283" t="s">
+      <c r="C67" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="D67" s="283"/>
-      <c r="E67" s="283"/>
-      <c r="F67" s="283"/>
-      <c r="G67" s="283"/>
-      <c r="H67" s="283"/>
-      <c r="I67" s="283"/>
-      <c r="J67" s="283"/>
-      <c r="K67" s="283"/>
-      <c r="L67" s="283"/>
-      <c r="M67" s="283"/>
-      <c r="N67" s="283"/>
-      <c r="O67" s="283"/>
-      <c r="P67" s="283"/>
-      <c r="Q67" s="283"/>
-      <c r="R67" s="284"/>
-      <c r="S67" s="294" t="s">
+      <c r="D67" s="96"/>
+      <c r="E67" s="96"/>
+      <c r="F67" s="96"/>
+      <c r="G67" s="96"/>
+      <c r="H67" s="96"/>
+      <c r="I67" s="96"/>
+      <c r="J67" s="96"/>
+      <c r="K67" s="96"/>
+      <c r="L67" s="96"/>
+      <c r="M67" s="96"/>
+      <c r="N67" s="96"/>
+      <c r="O67" s="96"/>
+      <c r="P67" s="96"/>
+      <c r="Q67" s="96"/>
+      <c r="R67" s="97"/>
+      <c r="S67" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="T67" s="295"/>
-      <c r="U67" s="295"/>
-      <c r="V67" s="296"/>
+      <c r="T67" s="120"/>
+      <c r="U67" s="120"/>
+      <c r="V67" s="121"/>
     </row>
     <row r="68" spans="2:22" s="2" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C68" s="283" t="s">
+      <c r="C68" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="D68" s="283"/>
-      <c r="E68" s="283"/>
-      <c r="F68" s="283"/>
-      <c r="G68" s="283"/>
-      <c r="H68" s="283"/>
-      <c r="I68" s="283"/>
-      <c r="J68" s="283"/>
-      <c r="K68" s="283"/>
-      <c r="L68" s="283"/>
-      <c r="M68" s="283"/>
-      <c r="N68" s="283"/>
-      <c r="O68" s="283"/>
-      <c r="P68" s="283"/>
-      <c r="Q68" s="283"/>
-      <c r="R68" s="284"/>
+      <c r="D68" s="96"/>
+      <c r="E68" s="96"/>
+      <c r="F68" s="96"/>
+      <c r="G68" s="96"/>
+      <c r="H68" s="96"/>
+      <c r="I68" s="96"/>
+      <c r="J68" s="96"/>
+      <c r="K68" s="96"/>
+      <c r="L68" s="96"/>
+      <c r="M68" s="96"/>
+      <c r="N68" s="96"/>
+      <c r="O68" s="96"/>
+      <c r="P68" s="96"/>
+      <c r="Q68" s="96"/>
+      <c r="R68" s="97"/>
       <c r="S68" s="52">
         <v>5</v>
       </c>
-      <c r="T68" s="285"/>
-      <c r="U68" s="285"/>
+      <c r="T68" s="104"/>
+      <c r="U68" s="104"/>
       <c r="V68" s="53"/>
     </row>
     <row r="69" spans="2:22" s="2" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B69" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C69" s="283" t="s">
+      <c r="C69" s="96" t="s">
         <v>79</v>
       </c>
-      <c r="D69" s="283"/>
-      <c r="E69" s="283"/>
-      <c r="F69" s="283"/>
-      <c r="G69" s="283"/>
-      <c r="H69" s="283"/>
-      <c r="I69" s="283"/>
-      <c r="J69" s="283"/>
-      <c r="K69" s="283"/>
-      <c r="L69" s="283"/>
-      <c r="M69" s="283"/>
-      <c r="N69" s="283"/>
-      <c r="O69" s="283"/>
-      <c r="P69" s="283"/>
-      <c r="Q69" s="283"/>
-      <c r="R69" s="284"/>
+      <c r="D69" s="96"/>
+      <c r="E69" s="96"/>
+      <c r="F69" s="96"/>
+      <c r="G69" s="96"/>
+      <c r="H69" s="96"/>
+      <c r="I69" s="96"/>
+      <c r="J69" s="96"/>
+      <c r="K69" s="96"/>
+      <c r="L69" s="96"/>
+      <c r="M69" s="96"/>
+      <c r="N69" s="96"/>
+      <c r="O69" s="96"/>
+      <c r="P69" s="96"/>
+      <c r="Q69" s="96"/>
+      <c r="R69" s="97"/>
       <c r="S69" s="11">
         <v>4</v>
       </c>
-      <c r="T69" s="286"/>
-      <c r="U69" s="286"/>
+      <c r="T69" s="98"/>
+      <c r="U69" s="98"/>
       <c r="V69" s="12"/>
     </row>
     <row r="70" spans="2:22" s="2" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B70" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C70" s="283" t="s">
+      <c r="C70" s="96" t="s">
         <v>81</v>
       </c>
-      <c r="D70" s="283"/>
-      <c r="E70" s="283"/>
-      <c r="F70" s="283"/>
-      <c r="G70" s="283"/>
-      <c r="H70" s="283"/>
-      <c r="I70" s="283"/>
-      <c r="J70" s="283"/>
-      <c r="K70" s="283"/>
-      <c r="L70" s="283"/>
-      <c r="M70" s="283"/>
-      <c r="N70" s="283"/>
-      <c r="O70" s="283"/>
-      <c r="P70" s="283"/>
-      <c r="Q70" s="283"/>
-      <c r="R70" s="284"/>
+      <c r="D70" s="96"/>
+      <c r="E70" s="96"/>
+      <c r="F70" s="96"/>
+      <c r="G70" s="96"/>
+      <c r="H70" s="96"/>
+      <c r="I70" s="96"/>
+      <c r="J70" s="96"/>
+      <c r="K70" s="96"/>
+      <c r="L70" s="96"/>
+      <c r="M70" s="96"/>
+      <c r="N70" s="96"/>
+      <c r="O70" s="96"/>
+      <c r="P70" s="96"/>
+      <c r="Q70" s="96"/>
+      <c r="R70" s="97"/>
       <c r="S70" s="11">
         <v>3</v>
       </c>
-      <c r="T70" s="286"/>
-      <c r="U70" s="286"/>
+      <c r="T70" s="98"/>
+      <c r="U70" s="98"/>
       <c r="V70" s="12"/>
     </row>
     <row r="71" spans="2:22" s="2" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B71" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C71" s="303" t="s">
+      <c r="C71" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="D71" s="303"/>
-      <c r="E71" s="303"/>
-      <c r="F71" s="303"/>
-      <c r="G71" s="303"/>
-      <c r="H71" s="303"/>
-      <c r="I71" s="303"/>
-      <c r="J71" s="303"/>
-      <c r="K71" s="303"/>
-      <c r="L71" s="303"/>
-      <c r="M71" s="303"/>
-      <c r="N71" s="303"/>
-      <c r="O71" s="303"/>
-      <c r="P71" s="303"/>
-      <c r="Q71" s="303"/>
-      <c r="R71" s="304"/>
+      <c r="D71" s="102"/>
+      <c r="E71" s="102"/>
+      <c r="F71" s="102"/>
+      <c r="G71" s="102"/>
+      <c r="H71" s="102"/>
+      <c r="I71" s="102"/>
+      <c r="J71" s="102"/>
+      <c r="K71" s="102"/>
+      <c r="L71" s="102"/>
+      <c r="M71" s="102"/>
+      <c r="N71" s="102"/>
+      <c r="O71" s="102"/>
+      <c r="P71" s="102"/>
+      <c r="Q71" s="102"/>
+      <c r="R71" s="103"/>
       <c r="S71" s="11">
         <v>2</v>
       </c>
-      <c r="T71" s="286"/>
-      <c r="U71" s="286"/>
+      <c r="T71" s="98"/>
+      <c r="U71" s="98"/>
       <c r="V71" s="12"/>
     </row>
     <row r="72" spans="2:22" s="2" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B72" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="283" t="s">
+      <c r="C72" s="96" t="s">
         <v>141</v>
       </c>
-      <c r="D72" s="283"/>
-      <c r="E72" s="283"/>
-      <c r="F72" s="283"/>
-      <c r="G72" s="283"/>
-      <c r="H72" s="283"/>
-      <c r="I72" s="283"/>
-      <c r="J72" s="283"/>
-      <c r="K72" s="283"/>
-      <c r="L72" s="283"/>
-      <c r="M72" s="283"/>
-      <c r="N72" s="283"/>
-      <c r="O72" s="283"/>
-      <c r="P72" s="283"/>
-      <c r="Q72" s="283"/>
-      <c r="R72" s="284"/>
+      <c r="D72" s="96"/>
+      <c r="E72" s="96"/>
+      <c r="F72" s="96"/>
+      <c r="G72" s="96"/>
+      <c r="H72" s="96"/>
+      <c r="I72" s="96"/>
+      <c r="J72" s="96"/>
+      <c r="K72" s="96"/>
+      <c r="L72" s="96"/>
+      <c r="M72" s="96"/>
+      <c r="N72" s="96"/>
+      <c r="O72" s="96"/>
+      <c r="P72" s="96"/>
+      <c r="Q72" s="96"/>
+      <c r="R72" s="97"/>
       <c r="S72" s="13">
         <v>1</v>
       </c>
-      <c r="T72" s="286"/>
-      <c r="U72" s="286"/>
+      <c r="T72" s="98"/>
+      <c r="U72" s="98"/>
       <c r="V72" s="14"/>
     </row>
     <row r="73" spans="2:22" s="2" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B73" s="20"/>
-      <c r="C73" s="283" t="s">
+      <c r="C73" s="96" t="s">
         <v>142</v>
       </c>
-      <c r="D73" s="283"/>
-      <c r="E73" s="283"/>
-      <c r="F73" s="283"/>
-      <c r="G73" s="283"/>
-      <c r="H73" s="283"/>
-      <c r="I73" s="283"/>
-      <c r="J73" s="283"/>
-      <c r="K73" s="283"/>
-      <c r="L73" s="283"/>
-      <c r="M73" s="283"/>
-      <c r="N73" s="283"/>
-      <c r="O73" s="283"/>
-      <c r="P73" s="283"/>
-      <c r="Q73" s="283"/>
-      <c r="R73" s="284"/>
+      <c r="D73" s="96"/>
+      <c r="E73" s="96"/>
+      <c r="F73" s="96"/>
+      <c r="G73" s="96"/>
+      <c r="H73" s="96"/>
+      <c r="I73" s="96"/>
+      <c r="J73" s="96"/>
+      <c r="K73" s="96"/>
+      <c r="L73" s="96"/>
+      <c r="M73" s="96"/>
+      <c r="N73" s="96"/>
+      <c r="O73" s="96"/>
+      <c r="P73" s="96"/>
+      <c r="Q73" s="96"/>
+      <c r="R73" s="97"/>
       <c r="S73" s="13">
         <v>0</v>
       </c>
-      <c r="T73" s="286"/>
-      <c r="U73" s="286"/>
+      <c r="T73" s="98"/>
+      <c r="U73" s="98"/>
       <c r="V73" s="14"/>
     </row>
     <row r="74" spans="2:22" s="2" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74" s="54"/>
-      <c r="C74" s="300"/>
-      <c r="D74" s="300"/>
-      <c r="E74" s="300"/>
-      <c r="F74" s="300"/>
-      <c r="G74" s="300"/>
-      <c r="H74" s="300"/>
-      <c r="I74" s="300"/>
-      <c r="J74" s="300"/>
-      <c r="K74" s="300"/>
-      <c r="L74" s="300"/>
-      <c r="M74" s="300"/>
-      <c r="N74" s="300"/>
-      <c r="O74" s="300"/>
-      <c r="P74" s="300"/>
-      <c r="Q74" s="300"/>
-      <c r="R74" s="301"/>
+      <c r="C74" s="99"/>
+      <c r="D74" s="99"/>
+      <c r="E74" s="99"/>
+      <c r="F74" s="99"/>
+      <c r="G74" s="99"/>
+      <c r="H74" s="99"/>
+      <c r="I74" s="99"/>
+      <c r="J74" s="99"/>
+      <c r="K74" s="99"/>
+      <c r="L74" s="99"/>
+      <c r="M74" s="99"/>
+      <c r="N74" s="99"/>
+      <c r="O74" s="99"/>
+      <c r="P74" s="99"/>
+      <c r="Q74" s="99"/>
+      <c r="R74" s="100"/>
       <c r="S74" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="T74" s="302" t="s">
+      <c r="T74" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="U74" s="302"/>
+      <c r="U74" s="101"/>
       <c r="V74" s="56" t="s">
         <v>44</v>
       </c>
@@ -6185,16 +6185,243 @@
     <row r="93" ht="13.05" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="271">
-    <mergeCell ref="C73:R73"/>
-    <mergeCell ref="T73:U73"/>
-    <mergeCell ref="C74:R74"/>
-    <mergeCell ref="T74:U74"/>
-    <mergeCell ref="C70:R70"/>
-    <mergeCell ref="T70:U70"/>
-    <mergeCell ref="C71:R71"/>
-    <mergeCell ref="T71:U71"/>
-    <mergeCell ref="C72:R72"/>
-    <mergeCell ref="T72:U72"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="N54:V54"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="U29:U30"/>
+    <mergeCell ref="V29:V30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B58:D59"/>
+    <mergeCell ref="E60:V60"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="E56:G56"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="B53:D56"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="B45:V45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="S29:S30"/>
+    <mergeCell ref="T29:T30"/>
+    <mergeCell ref="N53:V53"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="L29:L30"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="S44:U44"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="B11:B44"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:L11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="E65:V65"/>
+    <mergeCell ref="E66:V66"/>
+    <mergeCell ref="P63:V63"/>
+    <mergeCell ref="G63:K63"/>
+    <mergeCell ref="L63:O63"/>
+    <mergeCell ref="M64:V64"/>
+    <mergeCell ref="E64:L64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="B1:V1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:M2"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="O4:P5"/>
+    <mergeCell ref="Q4:V4"/>
+    <mergeCell ref="Q5:V5"/>
+    <mergeCell ref="I7:M8"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:V7"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="N3:N8"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:V9"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D5:M6"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="T8:V8"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:V6"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="D7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:I15"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:S15"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:R24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="C16:V16"/>
+    <mergeCell ref="C17:V22"/>
+    <mergeCell ref="T25:T26"/>
+    <mergeCell ref="U25:U26"/>
+    <mergeCell ref="V25:V26"/>
+    <mergeCell ref="T27:T28"/>
+    <mergeCell ref="U27:U28"/>
+    <mergeCell ref="V27:V28"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="S25:S26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="L27:L28"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="S27:S28"/>
+    <mergeCell ref="O31:V31"/>
+    <mergeCell ref="C32:D33"/>
+    <mergeCell ref="E32:L32"/>
+    <mergeCell ref="M32:N33"/>
+    <mergeCell ref="O32:V32"/>
+    <mergeCell ref="E33:L33"/>
+    <mergeCell ref="O33:V33"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:L31"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="E62:V62"/>
+    <mergeCell ref="N55:V55"/>
+    <mergeCell ref="N56:V56"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="T43:U43"/>
+    <mergeCell ref="T46:U46"/>
+    <mergeCell ref="T39:U39"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="T40:U40"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="O46:P46"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="T48:U48"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="E61:V61"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="T41:U41"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="P42:S42"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="O48:P48"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="J46:K46"/>
     <mergeCell ref="C68:R68"/>
     <mergeCell ref="T68:U68"/>
     <mergeCell ref="J3:M4"/>
@@ -6219,243 +6446,16 @@
     <mergeCell ref="N52:O52"/>
     <mergeCell ref="R47:S47"/>
     <mergeCell ref="T47:U47"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="O49:P49"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="T41:U41"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="P42:S42"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="O48:P48"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="T48:U48"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="E61:V61"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="E62:V62"/>
-    <mergeCell ref="N55:V55"/>
-    <mergeCell ref="N56:V56"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="T43:U43"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="T40:U40"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="O47:P47"/>
-    <mergeCell ref="O46:P46"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="O31:V31"/>
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="E32:L32"/>
-    <mergeCell ref="M32:N33"/>
-    <mergeCell ref="O32:V32"/>
-    <mergeCell ref="E33:L33"/>
-    <mergeCell ref="O33:V33"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="T27:T28"/>
-    <mergeCell ref="U27:U28"/>
-    <mergeCell ref="V27:V28"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="S25:S26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="K27:K28"/>
-    <mergeCell ref="L27:L28"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="S27:S28"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:R24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="C16:V16"/>
-    <mergeCell ref="C17:V22"/>
-    <mergeCell ref="T25:T26"/>
-    <mergeCell ref="U25:U26"/>
-    <mergeCell ref="V25:V26"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:I15"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:S15"/>
-    <mergeCell ref="T15:V15"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="I7:M8"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="Q7:V7"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="N3:N8"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:V9"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:M6"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="T8:V8"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:V6"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="D7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="B1:V1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:M2"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="O4:P5"/>
-    <mergeCell ref="Q4:V4"/>
-    <mergeCell ref="Q5:V5"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="E65:V65"/>
-    <mergeCell ref="E66:V66"/>
-    <mergeCell ref="P63:V63"/>
-    <mergeCell ref="G63:K63"/>
-    <mergeCell ref="L63:O63"/>
-    <mergeCell ref="M64:V64"/>
-    <mergeCell ref="E64:L64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:L31"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="B45:V45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="S29:S30"/>
-    <mergeCell ref="T29:T30"/>
-    <mergeCell ref="N53:V53"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="L29:L30"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="E53:G53"/>
-    <mergeCell ref="S44:U44"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="B11:B44"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:L11"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="N54:V54"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="U29:U30"/>
-    <mergeCell ref="V29:V30"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="B58:D59"/>
-    <mergeCell ref="E60:V60"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="E56:G56"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="B53:D56"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="C73:R73"/>
+    <mergeCell ref="T73:U73"/>
+    <mergeCell ref="C74:R74"/>
+    <mergeCell ref="T74:U74"/>
+    <mergeCell ref="C70:R70"/>
+    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="C71:R71"/>
+    <mergeCell ref="T71:U71"/>
+    <mergeCell ref="C72:R72"/>
+    <mergeCell ref="T72:U72"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
